--- a/data/SCHOOLS 2025.xlsx
+++ b/data/SCHOOLS 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FlorisKuipersADC\Python_Projects\Schooltuinen%20Amsterdam\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E07650C-76F6-4FE0-A047-EBE28199644C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63A7533-F734-40E2-895E-5297A22200F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5753D62C-6060-44DC-AE8B-171BC587F40A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="944">
   <si>
     <t>code</t>
   </si>
@@ -1995,9 +1995,6 @@
   </si>
   <si>
     <t>graag starten om 8:30 Continurooster tot: 14.15</t>
-  </si>
-  <si>
-    <t>graag tegelijk met onze andere groep Continurooster tot: 14.15</t>
   </si>
   <si>
     <t>Mont De Eilanden</t>
@@ -3412,13 +3409,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43430540-BBA7-4347-B81D-8C67916B1A6D}">
-  <dimension ref="A1:T307"/>
+  <dimension ref="A1:T304"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -14450,31 +14448,31 @@
         <v>12431</v>
       </c>
       <c r="B193" s="3">
-        <v>690772</v>
+        <v>692546</v>
       </c>
       <c r="C193" s="3">
-        <v>2638</v>
+        <v>2608</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F193" s="3">
-        <v>206341726</v>
+      <c r="F193" s="3" t="s">
+        <v>640</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="H193" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="J193" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K193" s="3" t="s">
         <v>57</v>
@@ -14482,23 +14480,21 @@
       <c r="L193" s="5"/>
       <c r="M193" s="6"/>
       <c r="N193" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="O193" s="3" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="P193" s="3" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="Q193" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R193" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="R193" s="5"/>
       <c r="S193" s="5"/>
       <c r="T193" s="3" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
     </row>
     <row r="194" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -14506,31 +14502,31 @@
         <v>12431</v>
       </c>
       <c r="B194" s="3">
-        <v>690773</v>
+        <v>692545</v>
       </c>
       <c r="C194" s="3">
-        <v>2638</v>
+        <v>2608</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F194" s="3">
-        <v>206341726</v>
+      <c r="F194" s="3" t="s">
+        <v>640</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="H194" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="J194" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K194" s="3" t="s">
         <v>57</v>
@@ -14538,23 +14534,21 @@
       <c r="L194" s="5"/>
       <c r="M194" s="6"/>
       <c r="N194" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="O194" s="3" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="P194" s="3" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="Q194" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R194" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="R194" s="5"/>
       <c r="S194" s="5"/>
       <c r="T194" s="3" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
     </row>
     <row r="195" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -14562,53 +14556,57 @@
         <v>12431</v>
       </c>
       <c r="B195" s="3">
-        <v>692546</v>
+        <v>692661</v>
       </c>
       <c r="C195" s="3">
-        <v>2608</v>
+        <v>6389</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="H195" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="J195" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K195" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L195" s="5"/>
-      <c r="M195" s="6"/>
+      <c r="L195" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M195" s="4"/>
       <c r="N195" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O195" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="P195" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q195" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R195" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="R195" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="S195" s="5"/>
       <c r="T195" s="3" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
     </row>
     <row r="196" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -14616,53 +14614,59 @@
         <v>12431</v>
       </c>
       <c r="B196" s="3">
-        <v>692545</v>
+        <v>692647</v>
       </c>
       <c r="C196" s="3">
-        <v>2608</v>
+        <v>6348</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="H196" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="J196" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K196" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L196" s="5"/>
-      <c r="M196" s="6"/>
+      <c r="L196" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="M196" s="4"/>
       <c r="N196" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O196" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="P196" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R196" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S196" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="Q196" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R196" s="5"/>
-      <c r="S196" s="5"/>
       <c r="T196" s="3" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
     </row>
     <row r="197" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -14670,57 +14674,55 @@
         <v>12431</v>
       </c>
       <c r="B197" s="3">
-        <v>692661</v>
+        <v>692507</v>
       </c>
       <c r="C197" s="3">
-        <v>6389</v>
+        <v>4030</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="H197" s="3">
         <v>6</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="J197" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K197" s="3" t="s">
         <v>57</v>
       </c>
       <c r="L197" s="3" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="M197" s="4"/>
       <c r="N197" s="3">
         <v>1</v>
       </c>
       <c r="O197" s="3" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="P197" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q197" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R197" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="R197" s="5"/>
       <c r="S197" s="5"/>
       <c r="T197" s="3" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
     </row>
     <row r="198" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -14728,115 +14730,111 @@
         <v>12431</v>
       </c>
       <c r="B198" s="3">
-        <v>692662</v>
+        <v>692671</v>
       </c>
       <c r="C198" s="3">
-        <v>6389</v>
+        <v>3670</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H198" s="3">
         <v>6</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="J198" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K198" s="3" t="s">
         <v>57</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="M198" s="4"/>
       <c r="N198" s="3">
         <v>1</v>
       </c>
       <c r="O198" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="P198" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="Q198" s="3" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="R198" s="5"/>
       <c r="S198" s="5"/>
       <c r="T198" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="199" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="199" spans="1:20" ht="210.5" x14ac:dyDescent="0.35">
       <c r="A199" s="3">
         <v>12431</v>
       </c>
       <c r="B199" s="3">
-        <v>692647</v>
+        <v>690717</v>
       </c>
       <c r="C199" s="3">
-        <v>6348</v>
+        <v>6502</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H199" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J199" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K199" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L199" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="M199" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="L199" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="M199" s="8"/>
       <c r="N199" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O199" s="3" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="P199" s="3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="Q199" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R199" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="S199" s="3" t="s">
-        <v>29</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="R199" s="5"/>
+      <c r="S199" s="5"/>
       <c r="T199" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="200" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -14844,55 +14842,55 @@
         <v>12431</v>
       </c>
       <c r="B200" s="3">
-        <v>692507</v>
+        <v>690718</v>
       </c>
       <c r="C200" s="3">
-        <v>4030</v>
+        <v>6502</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="H200" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I200" s="3" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="J200" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K200" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L200" s="3" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="M200" s="4"/>
       <c r="N200" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O200" s="3" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="P200" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q200" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="Q200" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="R200" s="5"/>
       <c r="S200" s="5"/>
       <c r="T200" s="3" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
     </row>
     <row r="201" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -14900,37 +14898,37 @@
         <v>12431</v>
       </c>
       <c r="B201" s="3">
-        <v>692671</v>
+        <v>692512</v>
       </c>
       <c r="C201" s="3">
-        <v>3670</v>
+        <v>4038</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="H201" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="J201" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K201" s="3" t="s">
         <v>57</v>
       </c>
       <c r="L201" s="3" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="M201" s="4"/>
       <c r="N201" s="3">
@@ -14940,71 +14938,75 @@
         <v>29</v>
       </c>
       <c r="P201" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q201" s="3" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R201" s="5"/>
       <c r="S201" s="5"/>
       <c r="T201" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="202" spans="1:20" ht="210.5" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="202" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="3">
         <v>12431</v>
       </c>
       <c r="B202" s="3">
-        <v>690717</v>
+        <v>692465</v>
       </c>
       <c r="C202" s="3">
-        <v>6502</v>
+        <v>6347</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H202" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="J202" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L202" s="7" t="s">
-        <v>663</v>
-      </c>
-      <c r="M202" s="8"/>
+        <v>626</v>
+      </c>
+      <c r="L202" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="M202" s="4"/>
       <c r="N202" s="3">
         <v>2</v>
       </c>
       <c r="O202" s="3" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="P202" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q202" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R202" s="5"/>
-      <c r="S202" s="5"/>
+        <v>63</v>
+      </c>
+      <c r="R202" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="S202" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="T202" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="203" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15012,55 +15014,59 @@
         <v>12431</v>
       </c>
       <c r="B203" s="3">
-        <v>690718</v>
+        <v>692466</v>
       </c>
       <c r="C203" s="3">
-        <v>6502</v>
+        <v>6347</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H203" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="J203" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K203" s="3" t="s">
-        <v>35</v>
+        <v>626</v>
       </c>
       <c r="L203" s="3" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="M203" s="4"/>
       <c r="N203" s="3">
         <v>2</v>
       </c>
       <c r="O203" s="3" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="P203" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q203" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R203" s="5"/>
-      <c r="S203" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="R203" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="S203" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="T203" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="204" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15068,55 +15074,49 @@
         <v>12431</v>
       </c>
       <c r="B204" s="3">
-        <v>692512</v>
+        <v>692672</v>
       </c>
       <c r="C204" s="3">
-        <v>4038</v>
+        <v>18925</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>95</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="G204" s="5"/>
       <c r="H204" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="J204" s="3">
-        <v>29</v>
-      </c>
-      <c r="K204" s="3" t="s">
-        <v>57</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K204" s="5"/>
       <c r="L204" s="3" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="M204" s="4"/>
       <c r="N204" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O204" s="3" t="s">
-        <v>29</v>
+        <v>679</v>
       </c>
       <c r="P204" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q204" s="3" t="s">
-        <v>113</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="Q204" s="5"/>
       <c r="R204" s="5"/>
       <c r="S204" s="5"/>
       <c r="T204" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
     </row>
     <row r="205" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15124,59 +15124,49 @@
         <v>12431</v>
       </c>
       <c r="B205" s="3">
-        <v>692465</v>
+        <v>692673</v>
       </c>
       <c r="C205" s="3">
-        <v>6347</v>
+        <v>18925</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="G205" s="3" t="s">
-        <v>33</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="G205" s="5"/>
       <c r="H205" s="3">
         <v>6</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="J205" s="3">
-        <v>26</v>
-      </c>
-      <c r="K205" s="3" t="s">
-        <v>626</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="K205" s="5"/>
       <c r="L205" s="3" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="M205" s="4"/>
       <c r="N205" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O205" s="3" t="s">
-        <v>27</v>
+        <v>682</v>
       </c>
       <c r="P205" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q205" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R205" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="S205" s="3" t="s">
-        <v>28</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="Q205" s="5"/>
+      <c r="R205" s="5"/>
+      <c r="S205" s="5"/>
       <c r="T205" s="3" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
     </row>
     <row r="206" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15184,59 +15174,49 @@
         <v>12431</v>
       </c>
       <c r="B206" s="3">
-        <v>692466</v>
+        <v>692674</v>
       </c>
       <c r="C206" s="3">
-        <v>6347</v>
+        <v>18925</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="G206" s="3" t="s">
-        <v>33</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="G206" s="5"/>
       <c r="H206" s="3">
         <v>6</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="J206" s="3">
-        <v>26</v>
-      </c>
-      <c r="K206" s="3" t="s">
-        <v>626</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K206" s="5"/>
       <c r="L206" s="3" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="M206" s="4"/>
       <c r="N206" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O206" s="3" t="s">
-        <v>27</v>
+        <v>685</v>
       </c>
       <c r="P206" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q206" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R206" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="S206" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="Q206" s="5"/>
+      <c r="R206" s="5"/>
+      <c r="S206" s="5"/>
       <c r="T206" s="3" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
     </row>
     <row r="207" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15244,49 +15224,59 @@
         <v>12431</v>
       </c>
       <c r="B207" s="3">
-        <v>692672</v>
+        <v>690726</v>
       </c>
       <c r="C207" s="3">
-        <v>18925</v>
+        <v>5397</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="G207" s="5"/>
+        <v>688</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="H207" s="3">
         <v>6</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="J207" s="3">
-        <v>18</v>
-      </c>
-      <c r="K207" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="K207" s="3" t="s">
+        <v>690</v>
+      </c>
       <c r="L207" s="3" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="M207" s="4"/>
       <c r="N207" s="3">
         <v>3</v>
       </c>
       <c r="O207" s="3" t="s">
-        <v>680</v>
+        <v>63</v>
       </c>
       <c r="P207" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="Q207" s="5"/>
-      <c r="R207" s="5"/>
-      <c r="S207" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="Q207" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R207" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S207" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="T207" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
     </row>
     <row r="208" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15294,49 +15284,59 @@
         <v>12431</v>
       </c>
       <c r="B208" s="3">
-        <v>692673</v>
+        <v>690727</v>
       </c>
       <c r="C208" s="3">
-        <v>18925</v>
+        <v>5397</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="G208" s="5"/>
+        <v>688</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="H208" s="3">
         <v>6</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="J208" s="3">
-        <v>20</v>
-      </c>
-      <c r="K208" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="K208" s="3" t="s">
+        <v>693</v>
+      </c>
       <c r="L208" s="3" t="s">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="M208" s="4"/>
       <c r="N208" s="3">
         <v>3</v>
       </c>
       <c r="O208" s="3" t="s">
-        <v>683</v>
+        <v>63</v>
       </c>
       <c r="P208" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="Q208" s="5"/>
-      <c r="R208" s="5"/>
-      <c r="S208" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="Q208" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R208" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S208" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="T208" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
     </row>
     <row r="209" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15344,49 +15344,59 @@
         <v>12431</v>
       </c>
       <c r="B209" s="3">
-        <v>692674</v>
+        <v>690728</v>
       </c>
       <c r="C209" s="3">
-        <v>18925</v>
+        <v>5397</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="G209" s="5"/>
+        <v>688</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="H209" s="3">
         <v>6</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="J209" s="3">
-        <v>17</v>
-      </c>
-      <c r="K209" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="K209" s="3" t="s">
+        <v>690</v>
+      </c>
       <c r="L209" s="3" t="s">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="M209" s="4"/>
       <c r="N209" s="3">
         <v>3</v>
       </c>
       <c r="O209" s="3" t="s">
-        <v>686</v>
+        <v>63</v>
       </c>
       <c r="P209" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="Q209" s="5"/>
-      <c r="R209" s="5"/>
-      <c r="S209" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="Q209" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R209" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S209" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="T209" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
     </row>
     <row r="210" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15394,59 +15404,55 @@
         <v>12431</v>
       </c>
       <c r="B210" s="3">
-        <v>690726</v>
+        <v>690777</v>
       </c>
       <c r="C210" s="3">
-        <v>5397</v>
+        <v>3677</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="H210" s="3">
         <v>6</v>
       </c>
       <c r="I210" s="3" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="J210" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K210" s="3" t="s">
-        <v>691</v>
+        <v>135</v>
       </c>
       <c r="L210" s="3" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="M210" s="4"/>
       <c r="N210" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O210" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="P210" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q210" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R210" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S210" s="3" t="s">
-        <v>63</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="R210" s="5"/>
+      <c r="S210" s="5"/>
       <c r="T210" s="3" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
     </row>
     <row r="211" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15454,59 +15460,55 @@
         <v>12431</v>
       </c>
       <c r="B211" s="3">
-        <v>690727</v>
+        <v>690779</v>
       </c>
       <c r="C211" s="3">
-        <v>5397</v>
+        <v>3677</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="H211" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I211" s="3" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="J211" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>694</v>
+        <v>129</v>
       </c>
       <c r="L211" s="3" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="M211" s="4"/>
       <c r="N211" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O211" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="P211" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q211" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R211" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S211" s="3" t="s">
-        <v>63</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="R211" s="5"/>
+      <c r="S211" s="5"/>
       <c r="T211" s="3" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
     </row>
     <row r="212" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15514,59 +15516,59 @@
         <v>12431</v>
       </c>
       <c r="B212" s="3">
-        <v>690728</v>
+        <v>692606</v>
       </c>
       <c r="C212" s="3">
-        <v>5397</v>
+        <v>3641</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="H212" s="3">
         <v>6</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="J212" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>691</v>
+        <v>57</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="M212" s="4"/>
       <c r="N212" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O212" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P212" s="3" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="Q212" s="3" t="s">
         <v>37</v>
       </c>
       <c r="R212" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S212" s="3" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="T212" s="3" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15574,55 +15576,53 @@
         <v>12431</v>
       </c>
       <c r="B213" s="3">
-        <v>690777</v>
+        <v>690697</v>
       </c>
       <c r="C213" s="3">
-        <v>3677</v>
+        <v>6356</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="E213" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H213" s="3">
+        <v>6</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="J213" s="3">
         <v>21</v>
       </c>
-      <c r="F213" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="G213" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H213" s="3">
-        <v>6</v>
-      </c>
-      <c r="I213" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="J213" s="3">
-        <v>27</v>
-      </c>
       <c r="K213" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="L213" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="M213" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="L213" s="5"/>
+      <c r="M213" s="6"/>
       <c r="N213" s="3">
         <v>2</v>
       </c>
       <c r="O213" s="3" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P213" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="Q213" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="R213" s="5"/>
       <c r="S213" s="5"/>
       <c r="T213" s="3" t="s">
-        <v>43</v>
+        <v>204</v>
       </c>
     </row>
     <row r="214" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15630,55 +15630,53 @@
         <v>12431</v>
       </c>
       <c r="B214" s="3">
-        <v>690779</v>
+        <v>690698</v>
       </c>
       <c r="C214" s="3">
-        <v>3677</v>
+        <v>6356</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="E214" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H214" s="3">
+        <v>6</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="J214" s="3">
         <v>21</v>
       </c>
-      <c r="F214" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H214" s="3">
-        <v>16</v>
-      </c>
-      <c r="I214" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="J214" s="3">
-        <v>25</v>
-      </c>
       <c r="K214" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="L214" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="M214" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="L214" s="5"/>
+      <c r="M214" s="6"/>
       <c r="N214" s="3">
         <v>2</v>
       </c>
       <c r="O214" s="3" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P214" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="Q214" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="R214" s="5"/>
       <c r="S214" s="5"/>
       <c r="T214" s="3" t="s">
-        <v>43</v>
+        <v>204</v>
       </c>
     </row>
     <row r="215" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15686,19 +15684,19 @@
         <v>12431</v>
       </c>
       <c r="B215" s="3">
-        <v>692606</v>
+        <v>690731</v>
       </c>
       <c r="C215" s="3">
-        <v>3641</v>
+        <v>4021</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>23</v>
@@ -15707,36 +15705,32 @@
         <v>6</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="J215" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K215" s="3" t="s">
         <v>57</v>
       </c>
       <c r="L215" s="3" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="M215" s="4"/>
       <c r="N215" s="3">
         <v>1</v>
       </c>
       <c r="O215" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P215" s="3" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="Q215" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R215" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="S215" s="3" t="s">
-        <v>27</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="R215" s="5"/>
+      <c r="S215" s="5"/>
       <c r="T215" s="3" t="s">
         <v>23</v>
       </c>
@@ -15746,19 +15740,19 @@
         <v>12431</v>
       </c>
       <c r="B216" s="3">
-        <v>690697</v>
+        <v>690755</v>
       </c>
       <c r="C216" s="3">
-        <v>6356</v>
+        <v>2625</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="G216" s="3" t="s">
         <v>204</v>
@@ -15767,27 +15761,29 @@
         <v>6</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="J216" s="3">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K216" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L216" s="5"/>
-      <c r="M216" s="6"/>
+        <v>379</v>
+      </c>
+      <c r="L216" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="M216" s="4"/>
       <c r="N216" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O216" s="3" t="s">
         <v>28</v>
       </c>
       <c r="P216" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="Q216" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="R216" s="5"/>
       <c r="S216" s="5"/>
@@ -15800,19 +15796,19 @@
         <v>12431</v>
       </c>
       <c r="B217" s="3">
-        <v>690698</v>
+        <v>690756</v>
       </c>
       <c r="C217" s="3">
-        <v>6356</v>
+        <v>2625</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>204</v>
@@ -15821,27 +15817,29 @@
         <v>6</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="J217" s="3">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K217" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L217" s="5"/>
-      <c r="M217" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="L217" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="M217" s="4"/>
       <c r="N217" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O217" s="3" t="s">
         <v>28</v>
       </c>
       <c r="P217" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="Q217" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="R217" s="5"/>
       <c r="S217" s="5"/>
@@ -15854,55 +15852,55 @@
         <v>12431</v>
       </c>
       <c r="B218" s="3">
-        <v>690731</v>
+        <v>690757</v>
       </c>
       <c r="C218" s="3">
-        <v>4021</v>
+        <v>2625</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
       <c r="H218" s="3">
         <v>6</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="J218" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K218" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L218" s="3" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="M218" s="4"/>
       <c r="N218" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O218" s="3" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="P218" s="3" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Q218" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="R218" s="5"/>
       <c r="S218" s="5"/>
       <c r="T218" s="3" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
     </row>
     <row r="219" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15910,55 +15908,57 @@
         <v>12431</v>
       </c>
       <c r="B219" s="3">
-        <v>690755</v>
+        <v>692565</v>
       </c>
       <c r="C219" s="3">
-        <v>2625</v>
+        <v>6508</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="H219" s="3">
         <v>6</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="J219" s="3">
         <v>28</v>
       </c>
       <c r="K219" s="3" t="s">
-        <v>379</v>
+        <v>57</v>
       </c>
       <c r="L219" s="3" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="M219" s="4"/>
       <c r="N219" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O219" s="3" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="P219" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="Q219" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R219" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="R219" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="S219" s="5"/>
       <c r="T219" s="3" t="s">
-        <v>204</v>
+        <v>43</v>
       </c>
     </row>
     <row r="220" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -15966,55 +15966,59 @@
         <v>12431</v>
       </c>
       <c r="B220" s="3">
-        <v>690756</v>
+        <v>690704</v>
       </c>
       <c r="C220" s="3">
-        <v>2625</v>
+        <v>7025</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>204</v>
+        <v>33</v>
       </c>
       <c r="H220" s="3">
         <v>6</v>
       </c>
       <c r="I220" s="3" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="J220" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K220" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L220" s="3" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="M220" s="4"/>
       <c r="N220" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O220" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P220" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q220" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R220" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S220" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P220" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q220" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R220" s="5"/>
-      <c r="S220" s="5"/>
       <c r="T220" s="3" t="s">
-        <v>204</v>
+        <v>33</v>
       </c>
     </row>
     <row r="221" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16022,401 +16026,397 @@
         <v>12431</v>
       </c>
       <c r="B221" s="3">
-        <v>690757</v>
+        <v>692530</v>
       </c>
       <c r="C221" s="3">
-        <v>2625</v>
+        <v>3679</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="H221" s="3">
         <v>6</v>
       </c>
       <c r="I221" s="3" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="J221" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K221" s="3" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="L221" s="3" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="M221" s="4"/>
       <c r="N221" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O221" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P221" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q221" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R221" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S221" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P221" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q221" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R221" s="5"/>
-      <c r="S221" s="5"/>
       <c r="T221" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="222" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="222" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
       <c r="A222" s="3">
         <v>12431</v>
       </c>
       <c r="B222" s="3">
-        <v>692565</v>
+        <v>692579</v>
       </c>
       <c r="C222" s="3">
-        <v>6508</v>
+        <v>6352</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="H222" s="3">
         <v>6</v>
       </c>
       <c r="I222" s="3" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="J222" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K222" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L222" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="M222" s="4"/>
+      <c r="L222" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="M222" s="8"/>
       <c r="N222" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O222" s="3" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="P222" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="Q222" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R222" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="R222" s="5"/>
       <c r="S222" s="5"/>
       <c r="T222" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="223" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="223" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
       <c r="A223" s="3">
         <v>12431</v>
       </c>
       <c r="B223" s="3">
-        <v>690704</v>
+        <v>692581</v>
       </c>
       <c r="C223" s="3">
-        <v>7025</v>
+        <v>6352</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="H223" s="3">
         <v>6</v>
       </c>
       <c r="I223" s="3" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="J223" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K223" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L223" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="M223" s="4"/>
+      <c r="L223" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="M223" s="8"/>
       <c r="N223" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O223" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="P223" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q223" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R223" s="5"/>
+      <c r="S223" s="5"/>
+      <c r="T223" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="224" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+      <c r="A224" s="3">
+        <v>12431</v>
+      </c>
+      <c r="B224" s="3">
+        <v>6925811</v>
+      </c>
+      <c r="C224" s="3">
+        <v>6352</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H224" s="3">
+        <v>6</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="J224" s="3">
+        <v>20</v>
+      </c>
+      <c r="K224" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L224" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="M224" s="8"/>
+      <c r="N224" s="3">
+        <v>2</v>
+      </c>
+      <c r="O224" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="R223" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="S223" s="3" t="s">
+      <c r="P224" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="T223" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="224" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A224" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B224" s="3">
-        <v>692530</v>
-      </c>
-      <c r="C224" s="3">
-        <v>3679</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="E224" s="3" t="s">
+      <c r="Q224" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R224" s="5"/>
+      <c r="S224" s="5"/>
+      <c r="T224" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="225" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A225" s="3">
+        <v>12431</v>
+      </c>
+      <c r="B225" s="3">
+        <v>690608</v>
+      </c>
+      <c r="C225" s="3">
+        <v>2637</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="E225" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F224" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="G224" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H224" s="3">
-        <v>6</v>
-      </c>
-      <c r="I224" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="J224" s="3">
-        <v>25</v>
-      </c>
-      <c r="K224" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L224" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="M224" s="4"/>
-      <c r="N224" s="3">
-        <v>1</v>
-      </c>
-      <c r="O224" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P224" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q224" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="R224" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S224" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="T224" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="225" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
-      <c r="A225" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B225" s="3">
-        <v>692579</v>
-      </c>
-      <c r="C225" s="3">
-        <v>6352</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="F225" s="3" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="H225" s="3">
         <v>6</v>
       </c>
       <c r="I225" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="J225" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K225" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L225" s="7" t="s">
-        <v>738</v>
-      </c>
-      <c r="M225" s="8"/>
+      <c r="L225" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="M225" s="4"/>
       <c r="N225" s="3">
         <v>2</v>
       </c>
       <c r="O225" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P225" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="P225" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="Q225" s="3" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="R225" s="5"/>
       <c r="S225" s="5"/>
       <c r="T225" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="226" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="226" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" s="3">
         <v>12431</v>
       </c>
       <c r="B226" s="3">
-        <v>692581</v>
+        <v>690609</v>
       </c>
       <c r="C226" s="3">
-        <v>6352</v>
+        <v>2637</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="H226" s="3">
         <v>6</v>
       </c>
       <c r="I226" s="3" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="J226" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K226" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L226" s="7" t="s">
-        <v>738</v>
-      </c>
-      <c r="M226" s="8"/>
+      <c r="L226" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="M226" s="4"/>
       <c r="N226" s="3">
         <v>2</v>
       </c>
       <c r="O226" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P226" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="P226" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="Q226" s="3" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="R226" s="5"/>
       <c r="S226" s="5"/>
       <c r="T226" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="227" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="227" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="3">
         <v>12431</v>
       </c>
       <c r="B227" s="3">
-        <v>6925811</v>
+        <v>692536</v>
       </c>
       <c r="C227" s="3">
-        <v>6352</v>
+        <v>6510</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="H227" s="3">
         <v>6</v>
       </c>
       <c r="I227" s="3" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="J227" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K227" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L227" s="7" t="s">
-        <v>738</v>
-      </c>
-      <c r="M227" s="8"/>
+        <v>748</v>
+      </c>
+      <c r="L227" s="5"/>
+      <c r="M227" s="6"/>
       <c r="N227" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O227" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P227" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q227" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R227" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S227" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="P227" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q227" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R227" s="5"/>
-      <c r="S227" s="5"/>
       <c r="T227" s="3" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
     </row>
     <row r="228" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16424,19 +16424,19 @@
         <v>12431</v>
       </c>
       <c r="B228" s="3">
-        <v>690608</v>
+        <v>675818</v>
       </c>
       <c r="C228" s="3">
-        <v>2637</v>
+        <v>2618</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="G228" s="3" t="s">
         <v>204</v>
@@ -16445,32 +16445,36 @@
         <v>6</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="J228" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K228" s="3" t="s">
         <v>57</v>
       </c>
       <c r="L228" s="3" t="s">
-        <v>744</v>
+        <v>188</v>
       </c>
       <c r="M228" s="4"/>
       <c r="N228" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O228" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P228" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q228" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P228" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q228" s="3" t="s">
+      <c r="R228" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="R228" s="5"/>
-      <c r="S228" s="5"/>
+      <c r="S228" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="T228" s="3" t="s">
         <v>204</v>
       </c>
@@ -16480,55 +16484,57 @@
         <v>12431</v>
       </c>
       <c r="B229" s="3">
-        <v>690609</v>
+        <v>692454</v>
       </c>
       <c r="C229" s="3">
-        <v>2637</v>
+        <v>3639</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="H229" s="3">
         <v>6</v>
       </c>
       <c r="I229" s="3" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="J229" s="3">
+        <v>17</v>
+      </c>
+      <c r="K229" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L229" s="5"/>
+      <c r="M229" s="6"/>
+      <c r="N229" s="3">
+        <v>3</v>
+      </c>
+      <c r="O229" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P229" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q229" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R229" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S229" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K229" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L229" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="M229" s="4"/>
-      <c r="N229" s="3">
-        <v>2</v>
-      </c>
-      <c r="O229" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P229" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q229" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R229" s="5"/>
-      <c r="S229" s="5"/>
       <c r="T229" s="3" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
     </row>
     <row r="230" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16536,57 +16542,57 @@
         <v>12431</v>
       </c>
       <c r="B230" s="3">
-        <v>692536</v>
+        <v>692453</v>
       </c>
       <c r="C230" s="3">
-        <v>6510</v>
+        <v>3639</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="H230" s="3">
         <v>6</v>
       </c>
       <c r="I230" s="3" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="J230" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K230" s="3" t="s">
-        <v>749</v>
+        <v>25</v>
       </c>
       <c r="L230" s="5"/>
       <c r="M230" s="6"/>
       <c r="N230" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O230" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="P230" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Q230" s="3" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="R230" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S230" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="S230" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="T230" s="3" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
     </row>
     <row r="231" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16594,59 +16600,57 @@
         <v>12431</v>
       </c>
       <c r="B231" s="3">
-        <v>675818</v>
+        <v>692455</v>
       </c>
       <c r="C231" s="3">
-        <v>2618</v>
+        <v>3639</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="H231" s="3">
         <v>6</v>
       </c>
       <c r="I231" s="3" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="J231" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K231" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L231" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="M231" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="L231" s="5"/>
+      <c r="M231" s="6"/>
       <c r="N231" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O231" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P231" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q231" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="R231" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S231" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P231" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q231" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R231" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="S231" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="T231" s="3" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
     </row>
     <row r="232" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16654,57 +16658,55 @@
         <v>12431</v>
       </c>
       <c r="B232" s="3">
-        <v>692454</v>
+        <v>692588</v>
       </c>
       <c r="C232" s="3">
-        <v>3639</v>
+        <v>3626</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>95</v>
+        <v>289</v>
       </c>
       <c r="H232" s="3">
         <v>6</v>
       </c>
       <c r="I232" s="3" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="J232" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K232" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L232" s="5"/>
-      <c r="M232" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="L232" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="M232" s="4"/>
       <c r="N232" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O232" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P232" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q232" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="Q232" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R232" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="S232" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="R232" s="5"/>
+      <c r="S232" s="5"/>
       <c r="T232" s="3" t="s">
-        <v>95</v>
+        <v>289</v>
       </c>
     </row>
     <row r="233" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16712,57 +16714,57 @@
         <v>12431</v>
       </c>
       <c r="B233" s="3">
-        <v>692453</v>
+        <v>692652</v>
       </c>
       <c r="C233" s="3">
-        <v>3639</v>
+        <v>3636</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="H233" s="3">
         <v>6</v>
       </c>
       <c r="I233" s="3" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="J233" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K233" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L233" s="5"/>
-      <c r="M233" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="L233" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="M233" s="10" t="s">
+        <v>765</v>
+      </c>
       <c r="N233" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O233" s="3" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="P233" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Q233" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="R233" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S233" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="R233" s="5"/>
+      <c r="S233" s="5"/>
       <c r="T233" s="3" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16770,57 +16772,55 @@
         <v>12431</v>
       </c>
       <c r="B234" s="3">
-        <v>692455</v>
+        <v>692659</v>
       </c>
       <c r="C234" s="3">
-        <v>3639</v>
+        <v>6430</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>754</v>
+        <v>767</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H234" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="J234" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K234" s="3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L234" s="5"/>
-      <c r="M234" s="6"/>
+      <c r="M234" s="4" t="s">
+        <v>769</v>
+      </c>
       <c r="N234" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O234" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P234" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q234" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="R234" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="S234" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="R234" s="5"/>
+      <c r="S234" s="5"/>
       <c r="T234" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="235" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16828,55 +16828,55 @@
         <v>12431</v>
       </c>
       <c r="B235" s="3">
-        <v>692588</v>
+        <v>692660</v>
       </c>
       <c r="C235" s="3">
-        <v>3626</v>
+        <v>3684</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>289</v>
+        <v>43</v>
       </c>
       <c r="H235" s="3">
         <v>6</v>
       </c>
       <c r="I235" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="J235" s="3">
-        <v>13</v>
-      </c>
-      <c r="K235" s="3" t="s">
-        <v>35</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="K235" s="5"/>
       <c r="L235" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="M235" s="4"/>
+        <v>773</v>
+      </c>
+      <c r="M235" s="10" t="s">
+        <v>774</v>
+      </c>
       <c r="N235" s="3">
         <v>1</v>
       </c>
       <c r="O235" s="3" t="s">
-        <v>28</v>
+        <v>775</v>
       </c>
       <c r="P235" s="3" t="s">
-        <v>48</v>
+        <v>680</v>
       </c>
       <c r="Q235" s="3" t="s">
-        <v>63</v>
+        <v>776</v>
       </c>
       <c r="R235" s="5"/>
       <c r="S235" s="5"/>
       <c r="T235" s="3" t="s">
-        <v>289</v>
+        <v>43</v>
       </c>
     </row>
     <row r="236" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16884,57 +16884,59 @@
         <v>12431</v>
       </c>
       <c r="B236" s="3">
-        <v>692652</v>
+        <v>690692</v>
       </c>
       <c r="C236" s="3">
-        <v>3636</v>
+        <v>6520</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>23</v>
+        <v>294</v>
       </c>
       <c r="H236" s="3">
         <v>6</v>
       </c>
       <c r="I236" s="3" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="J236" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K236" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L236" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="M236" s="10" t="s">
-        <v>766</v>
+        <v>57</v>
+      </c>
+      <c r="L236" s="5"/>
+      <c r="M236" s="11" t="s">
+        <v>769</v>
       </c>
       <c r="N236" s="3">
         <v>1</v>
       </c>
       <c r="O236" s="3" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="P236" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q236" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R236" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S236" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="Q236" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="R236" s="5"/>
-      <c r="S236" s="5"/>
       <c r="T236" s="3" t="s">
-        <v>23</v>
+        <v>294</v>
       </c>
     </row>
     <row r="237" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16942,55 +16944,61 @@
         <v>12431</v>
       </c>
       <c r="B237" s="3">
-        <v>692659</v>
+        <v>692489</v>
       </c>
       <c r="C237" s="3">
-        <v>6430</v>
+        <v>2631</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>767</v>
+        <v>780</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>768</v>
+        <v>781</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="H237" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I237" s="3" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
       <c r="J237" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K237" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L237" s="5"/>
-      <c r="M237" s="4" t="s">
-        <v>770</v>
+        <v>54</v>
+      </c>
+      <c r="L237" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="M237" s="10" t="s">
+        <v>783</v>
       </c>
       <c r="N237" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O237" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P237" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q237" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="P237" s="3" t="s">
+      <c r="R237" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S237" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q237" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="R237" s="5"/>
-      <c r="S237" s="5"/>
       <c r="T237" s="3" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
     </row>
     <row r="238" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -16998,55 +17006,61 @@
         <v>12431</v>
       </c>
       <c r="B238" s="3">
-        <v>692660</v>
+        <v>692488</v>
       </c>
       <c r="C238" s="3">
-        <v>3684</v>
+        <v>2631</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="H238" s="3">
         <v>6</v>
       </c>
       <c r="I238" s="3" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="J238" s="3">
-        <v>16</v>
-      </c>
-      <c r="K238" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="K238" s="3" t="s">
+        <v>379</v>
+      </c>
       <c r="L238" s="3" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="M238" s="10" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="N238" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O238" s="3" t="s">
-        <v>776</v>
+        <v>29</v>
       </c>
       <c r="P238" s="3" t="s">
-        <v>681</v>
+        <v>113</v>
       </c>
       <c r="Q238" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="R238" s="5"/>
-      <c r="S238" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="R238" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S238" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="T238" s="3" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
     </row>
     <row r="239" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17054,59 +17068,55 @@
         <v>12431</v>
       </c>
       <c r="B239" s="3">
-        <v>690692</v>
+        <v>692566</v>
       </c>
       <c r="C239" s="3">
-        <v>6520</v>
+        <v>3665</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>294</v>
+        <v>130</v>
       </c>
       <c r="H239" s="3">
         <v>6</v>
       </c>
       <c r="I239" s="3" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="J239" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K239" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L239" s="5"/>
-      <c r="M239" s="11" t="s">
-        <v>770</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L239" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="M239" s="4"/>
       <c r="N239" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O239" s="3" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="P239" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Q239" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R239" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="S239" s="3" t="s">
-        <v>29</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="R239" s="5"/>
+      <c r="S239" s="5"/>
       <c r="T239" s="3" t="s">
-        <v>294</v>
+        <v>130</v>
       </c>
     </row>
     <row r="240" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17114,61 +17124,55 @@
         <v>12431</v>
       </c>
       <c r="B240" s="3">
-        <v>692489</v>
+        <v>692567</v>
       </c>
       <c r="C240" s="3">
-        <v>2631</v>
+        <v>3665</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="E240" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H240" s="3">
+        <v>6</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="J240" s="3">
         <v>21</v>
       </c>
-      <c r="F240" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="G240" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H240" s="3">
-        <v>6</v>
-      </c>
-      <c r="I240" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="J240" s="3">
-        <v>15</v>
-      </c>
       <c r="K240" s="3" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="L240" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="M240" s="10" t="s">
-        <v>784</v>
-      </c>
+        <v>789</v>
+      </c>
+      <c r="M240" s="4"/>
       <c r="N240" s="3">
         <v>2</v>
       </c>
       <c r="O240" s="3" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="P240" s="3" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="Q240" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="R240" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S240" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="R240" s="5"/>
+      <c r="S240" s="5"/>
       <c r="T240" s="3" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
     </row>
     <row r="241" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17176,61 +17180,55 @@
         <v>12431</v>
       </c>
       <c r="B241" s="3">
-        <v>692488</v>
+        <v>675832</v>
       </c>
       <c r="C241" s="3">
-        <v>2631</v>
+        <v>4018</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="H241" s="3">
         <v>6</v>
       </c>
       <c r="I241" s="3" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="J241" s="3">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K241" s="3" t="s">
-        <v>379</v>
+        <v>57</v>
       </c>
       <c r="L241" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="M241" s="10" t="s">
-        <v>784</v>
-      </c>
+        <v>794</v>
+      </c>
+      <c r="M241" s="4"/>
       <c r="N241" s="3">
         <v>2</v>
       </c>
       <c r="O241" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="P241" s="3" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="Q241" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R241" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S241" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="R241" s="5"/>
+      <c r="S241" s="5"/>
       <c r="T241" s="3" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17238,55 +17236,55 @@
         <v>12431</v>
       </c>
       <c r="B242" s="3">
-        <v>692566</v>
+        <v>692504</v>
       </c>
       <c r="C242" s="3">
-        <v>3665</v>
+        <v>4018</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="H242" s="3">
         <v>6</v>
       </c>
       <c r="I242" s="3" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="J242" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K242" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="L242" s="3" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="M242" s="4"/>
       <c r="N242" s="3">
         <v>2</v>
       </c>
       <c r="O242" s="3" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="P242" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="Q242" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R242" s="5"/>
       <c r="S242" s="5"/>
       <c r="T242" s="3" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17294,55 +17292,57 @@
         <v>12431</v>
       </c>
       <c r="B243" s="3">
-        <v>692567</v>
+        <v>692543</v>
       </c>
       <c r="C243" s="3">
-        <v>3665</v>
+        <v>6501</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H243" s="3">
         <v>6</v>
       </c>
       <c r="I243" s="3" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="J243" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K243" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L243" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="M243" s="4"/>
+        <v>800</v>
+      </c>
+      <c r="L243" s="5"/>
+      <c r="M243" s="6"/>
       <c r="N243" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O243" s="3" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="P243" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q243" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R243" s="5"/>
-      <c r="S243" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="R243" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S243" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="T243" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="244" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17350,55 +17350,57 @@
         <v>12431</v>
       </c>
       <c r="B244" s="3">
-        <v>675832</v>
+        <v>690749</v>
       </c>
       <c r="C244" s="3">
-        <v>4018</v>
+        <v>6501</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="H244" s="3">
         <v>6</v>
       </c>
       <c r="I244" s="3" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="J244" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K244" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L244" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="M244" s="4"/>
+        <v>595</v>
+      </c>
+      <c r="L244" s="5"/>
+      <c r="M244" s="6"/>
       <c r="N244" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O244" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="P244" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q244" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R244" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="P244" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q244" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R244" s="5"/>
-      <c r="S244" s="5"/>
+      <c r="S244" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="T244" s="3" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
     </row>
     <row r="245" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17406,55 +17408,57 @@
         <v>12431</v>
       </c>
       <c r="B245" s="3">
-        <v>692504</v>
+        <v>690748</v>
       </c>
       <c r="C245" s="3">
-        <v>4018</v>
+        <v>6501</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="H245" s="3">
         <v>6</v>
       </c>
       <c r="I245" s="3" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="J245" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K245" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L245" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="M245" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="L245" s="5"/>
+      <c r="M245" s="6"/>
       <c r="N245" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O245" s="3" t="s">
         <v>49</v>
       </c>
       <c r="P245" s="3" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="Q245" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R245" s="5"/>
-      <c r="S245" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="R245" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S245" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="T245" s="3" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
     </row>
     <row r="246" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17462,57 +17466,61 @@
         <v>12431</v>
       </c>
       <c r="B246" s="3">
-        <v>692543</v>
+        <v>692491</v>
       </c>
       <c r="C246" s="3">
-        <v>6501</v>
+        <v>3645</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H246" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I246" s="3" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="J246" s="3">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K246" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="L246" s="5"/>
-      <c r="M246" s="6"/>
+        <v>379</v>
+      </c>
+      <c r="L246" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="M246" s="4" t="s">
+        <v>769</v>
+      </c>
       <c r="N246" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O246" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P246" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q246" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R246" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S246" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="P246" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q246" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R246" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S246" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="T246" s="3" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
     </row>
     <row r="247" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17520,57 +17528,61 @@
         <v>12431</v>
       </c>
       <c r="B247" s="3">
-        <v>690749</v>
+        <v>692493</v>
       </c>
       <c r="C247" s="3">
-        <v>6501</v>
+        <v>3645</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H247" s="3">
         <v>6</v>
       </c>
       <c r="I247" s="3" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="J247" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K247" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="L247" s="5"/>
-      <c r="M247" s="6"/>
+        <v>379</v>
+      </c>
+      <c r="L247" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="M247" s="4" t="s">
+        <v>769</v>
+      </c>
       <c r="N247" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O247" s="3" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="P247" s="3" t="s">
         <v>47</v>
       </c>
       <c r="Q247" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="R247" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="S247" s="3" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="T247" s="3" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
     </row>
     <row r="248" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17578,57 +17590,57 @@
         <v>12431</v>
       </c>
       <c r="B248" s="3">
-        <v>690748</v>
+        <v>690765</v>
       </c>
       <c r="C248" s="3">
-        <v>6501</v>
+        <v>3645</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H248" s="3">
         <v>6</v>
       </c>
       <c r="I248" s="3" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="J248" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K248" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="L248" s="5"/>
-      <c r="M248" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="L248" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="M248" s="4" t="s">
+        <v>769</v>
+      </c>
       <c r="N248" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O248" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="P248" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Q248" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R248" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S248" s="3" t="s">
-        <v>27</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="R248" s="5"/>
+      <c r="S248" s="5"/>
       <c r="T248" s="3" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
     </row>
     <row r="249" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17636,123 +17648,115 @@
         <v>12431</v>
       </c>
       <c r="B249" s="3">
-        <v>692491</v>
+        <v>692596</v>
       </c>
       <c r="C249" s="3">
-        <v>3645</v>
+        <v>4053</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>95</v>
+        <v>294</v>
       </c>
       <c r="H249" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I249" s="3" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="J249" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K249" s="3" t="s">
-        <v>379</v>
+        <v>57</v>
       </c>
       <c r="L249" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="M249" s="4" t="s">
-        <v>770</v>
+        <v>814</v>
+      </c>
+      <c r="M249" s="10" t="s">
+        <v>783</v>
       </c>
       <c r="N249" s="3">
         <v>2</v>
       </c>
       <c r="O249" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P249" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q249" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R249" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S249" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="R249" s="5"/>
+      <c r="S249" s="5"/>
       <c r="T249" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="250" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="250" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
       <c r="A250" s="3">
         <v>12431</v>
       </c>
       <c r="B250" s="3">
-        <v>692493</v>
+        <v>692665</v>
       </c>
       <c r="C250" s="3">
-        <v>3645</v>
+        <v>4053</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>95</v>
+        <v>294</v>
       </c>
       <c r="H250" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I250" s="3" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="J250" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K250" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="L250" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="M250" s="4" t="s">
-        <v>770</v>
+        <v>142</v>
+      </c>
+      <c r="L250" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="M250" s="11" t="s">
+        <v>765</v>
       </c>
       <c r="N250" s="3">
         <v>2</v>
       </c>
       <c r="O250" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="P250" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="Q250" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R250" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S250" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="R250" s="5"/>
+      <c r="S250" s="5"/>
       <c r="T250" s="3" t="s">
-        <v>95</v>
+        <v>294</v>
       </c>
     </row>
     <row r="251" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17760,57 +17764,57 @@
         <v>12431</v>
       </c>
       <c r="B251" s="3">
-        <v>690765</v>
+        <v>675823</v>
       </c>
       <c r="C251" s="3">
-        <v>3645</v>
+        <v>2630</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>804</v>
+        <v>817</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>805</v>
+        <v>818</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="H251" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I251" s="3" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="J251" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K251" s="3" t="s">
         <v>57</v>
       </c>
       <c r="L251" s="3" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="M251" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="N251" s="3">
         <v>1</v>
       </c>
       <c r="O251" s="3" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="P251" s="3" t="s">
         <v>47</v>
       </c>
       <c r="Q251" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="R251" s="5"/>
       <c r="S251" s="5"/>
       <c r="T251" s="3" t="s">
-        <v>95</v>
+        <v>204</v>
       </c>
     </row>
     <row r="252" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -17818,231 +17822,239 @@
         <v>12431</v>
       </c>
       <c r="B252" s="3">
-        <v>692596</v>
+        <v>692500</v>
       </c>
       <c r="C252" s="3">
-        <v>4053</v>
+        <v>8306</v>
       </c>
       <c r="D252" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F252" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="E252" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F252" s="3" t="s">
-        <v>813</v>
-      </c>
       <c r="G252" s="3" t="s">
-        <v>294</v>
+        <v>52</v>
       </c>
       <c r="H252" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I252" s="3" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="J252" s="3">
         <v>12</v>
       </c>
       <c r="K252" s="3" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="L252" s="3" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="M252" s="10" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="N252" s="3">
         <v>2</v>
       </c>
       <c r="O252" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P252" s="3" t="s">
         <v>38</v>
       </c>
       <c r="Q252" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R252" s="5"/>
       <c r="S252" s="5"/>
       <c r="T252" s="3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="253" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="3">
         <v>12431</v>
       </c>
       <c r="B253" s="3">
-        <v>692665</v>
+        <v>692501</v>
       </c>
       <c r="C253" s="3">
-        <v>4053</v>
+        <v>8306</v>
       </c>
       <c r="D253" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F253" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="E253" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F253" s="3" t="s">
-        <v>813</v>
-      </c>
       <c r="G253" s="3" t="s">
-        <v>294</v>
+        <v>52</v>
       </c>
       <c r="H253" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I253" s="3" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="J253" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K253" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="L253" s="7" t="s">
-        <v>817</v>
-      </c>
-      <c r="M253" s="11" t="s">
-        <v>766</v>
+        <v>25</v>
+      </c>
+      <c r="L253" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="M253" s="10" t="s">
+        <v>826</v>
       </c>
       <c r="N253" s="3">
         <v>2</v>
       </c>
       <c r="O253" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="P253" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q253" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="R253" s="5"/>
       <c r="S253" s="5"/>
       <c r="T253" s="3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="254" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20" ht="180.5" x14ac:dyDescent="0.35">
       <c r="A254" s="3">
         <v>12431</v>
       </c>
       <c r="B254" s="3">
-        <v>675823</v>
+        <v>692495</v>
       </c>
       <c r="C254" s="3">
-        <v>2630</v>
+        <v>4057</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="H254" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I254" s="3" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="J254" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K254" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L254" s="3" t="s">
-        <v>821</v>
+        <v>379</v>
+      </c>
+      <c r="L254" s="7" t="s">
+        <v>830</v>
       </c>
       <c r="M254" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="N254" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O254" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P254" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q254" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R254" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S254" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="P254" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q254" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R254" s="5"/>
-      <c r="S254" s="5"/>
       <c r="T254" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="255" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20" ht="165.5" x14ac:dyDescent="0.35">
       <c r="A255" s="3">
         <v>12431</v>
       </c>
       <c r="B255" s="3">
-        <v>692500</v>
+        <v>692497</v>
       </c>
       <c r="C255" s="3">
-        <v>8306</v>
+        <v>4057</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="H255" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I255" s="3" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="J255" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K255" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L255" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="M255" s="10" t="s">
-        <v>770</v>
+        <v>379</v>
+      </c>
+      <c r="L255" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="M255" s="4" t="s">
+        <v>769</v>
       </c>
       <c r="N255" s="3">
         <v>2</v>
       </c>
       <c r="O255" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P255" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P255" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="Q255" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R255" s="5"/>
-      <c r="S255" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="R255" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="S255" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="T255" s="3" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
     </row>
     <row r="256" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18050,181 +18062,181 @@
         <v>12431</v>
       </c>
       <c r="B256" s="3">
-        <v>692501</v>
+        <v>690768</v>
       </c>
       <c r="C256" s="3">
-        <v>8306</v>
+        <v>5493</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>822</v>
+        <v>833</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="H256" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I256" s="3" t="s">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="J256" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K256" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="L256" s="3" t="s">
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="M256" s="10" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="N256" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O256" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="P256" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q256" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="Q256" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="R256" s="5"/>
       <c r="S256" s="5"/>
       <c r="T256" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="257" spans="1:20" ht="180.5" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="257" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
       <c r="A257" s="3">
         <v>12431</v>
       </c>
       <c r="B257" s="3">
-        <v>692495</v>
+        <v>690774</v>
       </c>
       <c r="C257" s="3">
-        <v>4057</v>
+        <v>6475</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="H257" s="3">
         <v>6</v>
       </c>
       <c r="I257" s="3" t="s">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="J257" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K257" s="3" t="s">
-        <v>379</v>
+        <v>57</v>
       </c>
       <c r="L257" s="7" t="s">
-        <v>831</v>
-      </c>
-      <c r="M257" s="4" t="s">
-        <v>770</v>
+        <v>841</v>
+      </c>
+      <c r="M257" s="8" t="s">
+        <v>769</v>
       </c>
       <c r="N257" s="3">
         <v>2</v>
       </c>
       <c r="O257" s="3" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="P257" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q257" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R257" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q257" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R257" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="S257" s="3" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="T257" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="258" spans="1:20" ht="165.5" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="258" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" s="3">
         <v>12431</v>
       </c>
       <c r="B258" s="3">
-        <v>692497</v>
+        <v>692460</v>
       </c>
       <c r="C258" s="3">
-        <v>4057</v>
+        <v>6475</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="H258" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I258" s="3" t="s">
-        <v>832</v>
+        <v>842</v>
       </c>
       <c r="J258" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K258" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="L258" s="7" t="s">
-        <v>833</v>
+        <v>57</v>
+      </c>
+      <c r="L258" s="3" t="s">
+        <v>843</v>
       </c>
       <c r="M258" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="N258" s="3">
         <v>2</v>
       </c>
       <c r="O258" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="P258" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q258" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R258" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="P258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q258" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="R258" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="S258" s="3" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="T258" s="3" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
     </row>
     <row r="259" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18232,119 +18244,115 @@
         <v>12431</v>
       </c>
       <c r="B259" s="3">
-        <v>690768</v>
+        <v>692578</v>
       </c>
       <c r="C259" s="3">
-        <v>5493</v>
+        <v>6340</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="H259" s="3">
         <v>6</v>
       </c>
       <c r="I259" s="3" t="s">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="J259" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K259" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L259" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="M259" s="10" t="s">
-        <v>838</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="L259" s="5"/>
+      <c r="M259" s="6"/>
       <c r="N259" s="3">
         <v>1</v>
       </c>
       <c r="O259" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P259" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q259" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R259" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="P259" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q259" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R259" s="5"/>
       <c r="S259" s="5"/>
       <c r="T259" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="260" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="260" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="3">
         <v>12431</v>
       </c>
       <c r="B260" s="3">
-        <v>690774</v>
+        <v>692605</v>
       </c>
       <c r="C260" s="3">
-        <v>6475</v>
+        <v>3617</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="H260" s="3">
         <v>6</v>
       </c>
       <c r="I260" s="3" t="s">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="J260" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K260" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L260" s="7" t="s">
-        <v>842</v>
-      </c>
-      <c r="M260" s="8" t="s">
-        <v>770</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="L260" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="M260" s="4"/>
       <c r="N260" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O260" s="3" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="P260" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="Q260" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="R260" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S260" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="S260" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="T260" s="3" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="261" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18352,61 +18360,53 @@
         <v>12431</v>
       </c>
       <c r="B261" s="3">
-        <v>692460</v>
+        <v>690644</v>
       </c>
       <c r="C261" s="3">
-        <v>6475</v>
+        <v>6355</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>839</v>
+        <v>852</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="H261" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I261" s="3" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="J261" s="3">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K261" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L261" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="M261" s="4" t="s">
-        <v>770</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="L261" s="5"/>
+      <c r="M261" s="6"/>
       <c r="N261" s="3">
         <v>2</v>
       </c>
       <c r="O261" s="3" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="P261" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="Q261" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R261" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S261" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="R261" s="5"/>
+      <c r="S261" s="5"/>
       <c r="T261" s="3" t="s">
-        <v>122</v>
+        <v>33</v>
       </c>
     </row>
     <row r="262" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18414,55 +18414,55 @@
         <v>12431</v>
       </c>
       <c r="B262" s="3">
-        <v>692578</v>
+        <v>690645</v>
       </c>
       <c r="C262" s="3">
-        <v>6340</v>
+        <v>6355</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>204</v>
+        <v>33</v>
       </c>
       <c r="H262" s="3">
         <v>6</v>
       </c>
       <c r="I262" s="3" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="J262" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K262" s="3" t="s">
-        <v>848</v>
-      </c>
-      <c r="L262" s="5"/>
-      <c r="M262" s="6"/>
+        <v>365</v>
+      </c>
+      <c r="L262" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="M262" s="4"/>
       <c r="N262" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O262" s="3" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="P262" s="3" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="Q262" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R262" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="R262" s="5"/>
       <c r="S262" s="5"/>
       <c r="T262" s="3" t="s">
-        <v>204</v>
+        <v>33</v>
       </c>
     </row>
     <row r="263" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18470,19 +18470,19 @@
         <v>12431</v>
       </c>
       <c r="B263" s="3">
-        <v>692605</v>
+        <v>690737</v>
       </c>
       <c r="C263" s="3">
-        <v>3617</v>
+        <v>4031</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="G263" s="3" t="s">
         <v>140</v>
@@ -18491,35 +18491,35 @@
         <v>6</v>
       </c>
       <c r="I263" s="3" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="J263" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K263" s="3" t="s">
-        <v>582</v>
+        <v>57</v>
       </c>
       <c r="L263" s="3" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="M263" s="4"/>
       <c r="N263" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O263" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="P263" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="Q263" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R263" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="S263" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="R263" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="S263" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="T263" s="3" t="s">
         <v>140</v>
@@ -18530,53 +18530,59 @@
         <v>12431</v>
       </c>
       <c r="B264" s="3">
-        <v>690644</v>
+        <v>690738</v>
       </c>
       <c r="C264" s="3">
-        <v>6355</v>
+        <v>4031</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="H264" s="3">
         <v>6</v>
       </c>
       <c r="I264" s="3" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="J264" s="3">
         <v>23</v>
       </c>
       <c r="K264" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="L264" s="5"/>
-      <c r="M264" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="L264" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="M264" s="4"/>
       <c r="N264" s="3">
         <v>2</v>
       </c>
       <c r="O264" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="P264" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="Q264" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R264" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="S264" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R264" s="5"/>
-      <c r="S264" s="5"/>
       <c r="T264" s="3" t="s">
-        <v>33</v>
+        <v>140</v>
       </c>
     </row>
     <row r="265" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18584,55 +18590,59 @@
         <v>12431</v>
       </c>
       <c r="B265" s="3">
-        <v>690645</v>
+        <v>690619</v>
       </c>
       <c r="C265" s="3">
-        <v>6355</v>
+        <v>3623</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>33</v>
+        <v>289</v>
       </c>
       <c r="H265" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I265" s="3" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="J265" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K265" s="3" t="s">
-        <v>365</v>
+        <v>25</v>
       </c>
       <c r="L265" s="3" t="s">
-        <v>857</v>
+        <v>571</v>
       </c>
       <c r="M265" s="4"/>
       <c r="N265" s="3">
         <v>2</v>
       </c>
       <c r="O265" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="P265" s="3" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="Q265" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R265" s="5"/>
-      <c r="S265" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="R265" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S265" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="T265" s="3" t="s">
-        <v>33</v>
+        <v>289</v>
       </c>
     </row>
     <row r="266" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18640,59 +18650,59 @@
         <v>12431</v>
       </c>
       <c r="B266" s="3">
-        <v>690737</v>
+        <v>690620</v>
       </c>
       <c r="C266" s="3">
-        <v>4031</v>
+        <v>3623</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="H266" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I266" s="3" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="J266" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K266" s="3" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="L266" s="3" t="s">
-        <v>861</v>
+        <v>571</v>
       </c>
       <c r="M266" s="4"/>
       <c r="N266" s="3">
         <v>2</v>
       </c>
       <c r="O266" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P266" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q266" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="P266" s="3" t="s">
+      <c r="R266" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q266" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="R266" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="S266" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="T266" s="3" t="s">
-        <v>140</v>
+        <v>289</v>
       </c>
     </row>
     <row r="267" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18700,41 +18710,39 @@
         <v>12431</v>
       </c>
       <c r="B267" s="3">
-        <v>690738</v>
+        <v>690640</v>
       </c>
       <c r="C267" s="3">
-        <v>4031</v>
+        <v>6515</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="H267" s="3">
         <v>6</v>
       </c>
       <c r="I267" s="3" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="J267" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K267" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L267" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="M267" s="4"/>
+        <v>869</v>
+      </c>
+      <c r="L267" s="5"/>
+      <c r="M267" s="6"/>
       <c r="N267" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O267" s="3" t="s">
         <v>55</v>
@@ -18743,16 +18751,12 @@
         <v>47</v>
       </c>
       <c r="Q267" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="R267" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="S267" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="R267" s="5"/>
+      <c r="S267" s="5"/>
       <c r="T267" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="268" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18760,59 +18764,59 @@
         <v>12431</v>
       </c>
       <c r="B268" s="3">
-        <v>690619</v>
+        <v>692597</v>
       </c>
       <c r="C268" s="3">
-        <v>3623</v>
+        <v>17358</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>289</v>
+        <v>43</v>
       </c>
       <c r="H268" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I268" s="3" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="J268" s="3">
         <v>26</v>
       </c>
       <c r="K268" s="3" t="s">
-        <v>25</v>
+        <v>873</v>
       </c>
       <c r="L268" s="3" t="s">
-        <v>571</v>
+        <v>874</v>
       </c>
       <c r="M268" s="4"/>
       <c r="N268" s="3">
         <v>2</v>
       </c>
       <c r="O268" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P268" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q268" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="R268" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q268" s="3" t="s">
+      <c r="S268" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="R268" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="S268" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="T268" s="3" t="s">
-        <v>289</v>
+        <v>43</v>
       </c>
     </row>
     <row r="269" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18820,59 +18824,57 @@
         <v>12431</v>
       </c>
       <c r="B269" s="3">
-        <v>690620</v>
+        <v>692598</v>
       </c>
       <c r="C269" s="3">
-        <v>3623</v>
+        <v>17358</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>289</v>
+        <v>43</v>
       </c>
       <c r="H269" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I269" s="3" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="J269" s="3">
         <v>26</v>
       </c>
       <c r="K269" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L269" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="M269" s="4"/>
+        <v>873</v>
+      </c>
+      <c r="L269" s="5"/>
+      <c r="M269" s="6"/>
       <c r="N269" s="3">
         <v>2</v>
       </c>
       <c r="O269" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P269" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q269" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="R269" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q269" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R269" s="3" t="s">
+      <c r="S269" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="S269" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="T269" s="3" t="s">
-        <v>289</v>
+        <v>43</v>
       </c>
     </row>
     <row r="270" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18880,53 +18882,59 @@
         <v>12431</v>
       </c>
       <c r="B270" s="3">
-        <v>690640</v>
+        <v>692479</v>
       </c>
       <c r="C270" s="3">
-        <v>6515</v>
+        <v>3618</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>122</v>
+        <v>289</v>
       </c>
       <c r="H270" s="3">
         <v>6</v>
       </c>
       <c r="I270" s="3" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
       <c r="J270" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K270" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="L270" s="5"/>
-      <c r="M270" s="6"/>
+        <v>879</v>
+      </c>
+      <c r="L270" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="M270" s="4"/>
       <c r="N270" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O270" s="3" t="s">
         <v>55</v>
       </c>
       <c r="P270" s="3" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Q270" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="R270" s="5"/>
-      <c r="S270" s="5"/>
+      <c r="R270" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S270" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="T270" s="3" t="s">
-        <v>122</v>
+        <v>289</v>
       </c>
     </row>
     <row r="271" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18934,59 +18942,59 @@
         <v>12431</v>
       </c>
       <c r="B271" s="3">
-        <v>692597</v>
+        <v>692478</v>
       </c>
       <c r="C271" s="3">
-        <v>17358</v>
+        <v>3618</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>43</v>
+        <v>289</v>
       </c>
       <c r="H271" s="3">
         <v>6</v>
       </c>
       <c r="I271" s="3" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="J271" s="3">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K271" s="3" t="s">
-        <v>874</v>
+        <v>142</v>
       </c>
       <c r="L271" s="3" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="M271" s="4"/>
       <c r="N271" s="3">
         <v>2</v>
       </c>
       <c r="O271" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="P271" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="Q271" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R271" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S271" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="T271" s="3" t="s">
-        <v>43</v>
+        <v>289</v>
       </c>
     </row>
     <row r="272" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -18994,57 +19002,59 @@
         <v>12431</v>
       </c>
       <c r="B272" s="3">
-        <v>692598</v>
+        <v>675825</v>
       </c>
       <c r="C272" s="3">
-        <v>17358</v>
+        <v>2626</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>43</v>
+        <v>204</v>
       </c>
       <c r="H272" s="3">
         <v>6</v>
       </c>
       <c r="I272" s="3" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="J272" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K272" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="L272" s="5"/>
-      <c r="M272" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="L272" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="M272" s="4"/>
       <c r="N272" s="3">
         <v>2</v>
       </c>
       <c r="O272" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="P272" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q272" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R272" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S272" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q272" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="R272" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S272" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="T272" s="3" t="s">
-        <v>43</v>
+        <v>204</v>
       </c>
     </row>
     <row r="273" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19052,59 +19062,59 @@
         <v>12431</v>
       </c>
       <c r="B273" s="3">
-        <v>692479</v>
+        <v>675824</v>
       </c>
       <c r="C273" s="3">
-        <v>3618</v>
+        <v>2626</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="H273" s="3">
         <v>6</v>
       </c>
       <c r="I273" s="3" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="J273" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K273" s="3" t="s">
-        <v>880</v>
+        <v>35</v>
       </c>
       <c r="L273" s="3" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="M273" s="4"/>
       <c r="N273" s="3">
         <v>2</v>
       </c>
       <c r="O273" s="3" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="P273" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q273" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q273" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="R273" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S273" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="T273" s="3" t="s">
-        <v>289</v>
+        <v>204</v>
       </c>
     </row>
     <row r="274" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19112,119 +19122,111 @@
         <v>12431</v>
       </c>
       <c r="B274" s="3">
-        <v>692478</v>
+        <v>692613</v>
       </c>
       <c r="C274" s="3">
-        <v>3618</v>
+        <v>10486</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>289</v>
+        <v>33</v>
       </c>
       <c r="H274" s="3">
         <v>6</v>
       </c>
       <c r="I274" s="3" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="J274" s="3">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K274" s="3" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="L274" s="3" t="s">
-        <v>883</v>
+        <v>188</v>
       </c>
       <c r="M274" s="4"/>
       <c r="N274" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O274" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P274" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q274" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="P274" s="3" t="s">
+      <c r="R274" s="5"/>
+      <c r="S274" s="5"/>
+      <c r="T274" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="275" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+      <c r="A275" s="3">
+        <v>12431</v>
+      </c>
+      <c r="B275" s="3">
+        <v>690806</v>
+      </c>
+      <c r="C275" s="3">
+        <v>6713</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H275" s="3">
+        <v>6</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="J275" s="3">
         <v>28</v>
       </c>
-      <c r="Q274" s="3" t="s">
+      <c r="K275" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L275" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="M275" s="8"/>
+      <c r="N275" s="3">
+        <v>1</v>
+      </c>
+      <c r="O275" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="R274" s="3" t="s">
+      <c r="P275" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="S274" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="T274" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="275" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A275" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B275" s="3">
-        <v>675825</v>
-      </c>
-      <c r="C275" s="3">
-        <v>2626</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="E275" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F275" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="G275" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H275" s="3">
-        <v>6</v>
-      </c>
-      <c r="I275" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="J275" s="3">
-        <v>17</v>
-      </c>
-      <c r="K275" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L275" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="M275" s="4"/>
-      <c r="N275" s="3">
-        <v>2</v>
-      </c>
-      <c r="O275" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P275" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="Q275" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R275" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S275" s="3" t="s">
-        <v>49</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="R275" s="5"/>
+      <c r="S275" s="5"/>
       <c r="T275" s="3" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
     </row>
     <row r="276" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19232,59 +19234,59 @@
         <v>12431</v>
       </c>
       <c r="B276" s="3">
-        <v>675824</v>
+        <v>692644</v>
       </c>
       <c r="C276" s="3">
-        <v>2626</v>
+        <v>10220</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="H276" s="3">
         <v>6</v>
       </c>
       <c r="I276" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="J276" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K276" s="3" t="s">
         <v>35</v>
       </c>
       <c r="L276" s="3" t="s">
-        <v>887</v>
+        <v>188</v>
       </c>
       <c r="M276" s="4"/>
       <c r="N276" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O276" s="3" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="P276" s="3" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="Q276" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R276" s="3" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="S276" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="T276" s="3" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
     </row>
     <row r="277" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19292,111 +19294,123 @@
         <v>12431</v>
       </c>
       <c r="B277" s="3">
-        <v>692613</v>
+        <v>690677</v>
       </c>
       <c r="C277" s="3">
-        <v>10486</v>
+        <v>3682</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="H277" s="3">
         <v>6</v>
       </c>
       <c r="I277" s="3" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="J277" s="3">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="K277" s="3" t="s">
         <v>57</v>
       </c>
       <c r="L277" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="M277" s="4"/>
+        <v>901</v>
+      </c>
+      <c r="M277" s="10" t="s">
+        <v>783</v>
+      </c>
       <c r="N277" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O277" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P277" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q277" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R277" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S277" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="P277" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q277" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R277" s="5"/>
-      <c r="S277" s="5"/>
       <c r="T277" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="278" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="278" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A278" s="3">
         <v>12431</v>
       </c>
       <c r="B278" s="3">
-        <v>690806</v>
+        <v>690678</v>
       </c>
       <c r="C278" s="3">
-        <v>6713</v>
+        <v>3682</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="H278" s="3">
         <v>6</v>
       </c>
       <c r="I278" s="3" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="J278" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K278" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L278" s="7" t="s">
-        <v>895</v>
-      </c>
-      <c r="M278" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="L278" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="M278" s="10" t="s">
+        <v>783</v>
+      </c>
       <c r="N278" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O278" s="3" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="P278" s="3" t="s">
         <v>37</v>
       </c>
       <c r="Q278" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R278" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="R278" s="5"/>
-      <c r="S278" s="5"/>
+      <c r="S278" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="T278" s="3" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
     </row>
     <row r="279" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19404,59 +19418,57 @@
         <v>12431</v>
       </c>
       <c r="B279" s="3">
-        <v>692644</v>
+        <v>692607</v>
       </c>
       <c r="C279" s="3">
-        <v>10220</v>
+        <v>6364</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>85</v>
+        <v>294</v>
       </c>
       <c r="H279" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I279" s="3" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="J279" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="K279" s="3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="L279" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="M279" s="4"/>
+        <v>906</v>
+      </c>
+      <c r="M279" s="10" t="s">
+        <v>783</v>
+      </c>
       <c r="N279" s="3">
         <v>1</v>
       </c>
       <c r="O279" s="3" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="P279" s="3" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="Q279" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R279" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="S279" s="3" t="s">
-        <v>38</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="R279" s="5"/>
+      <c r="S279" s="5"/>
       <c r="T279" s="3" t="s">
-        <v>85</v>
+        <v>294</v>
       </c>
     </row>
     <row r="280" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19464,19 +19476,19 @@
         <v>12431</v>
       </c>
       <c r="B280" s="3">
-        <v>690677</v>
+        <v>692471</v>
       </c>
       <c r="C280" s="3">
-        <v>3682</v>
+        <v>3653</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="G280" s="3" t="s">
         <v>130</v>
@@ -19485,38 +19497,32 @@
         <v>6</v>
       </c>
       <c r="I280" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="J280" s="3">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="K280" s="3" t="s">
-        <v>57</v>
+        <v>910</v>
       </c>
       <c r="L280" s="3" t="s">
-        <v>902</v>
-      </c>
-      <c r="M280" s="10" t="s">
-        <v>784</v>
-      </c>
+        <v>911</v>
+      </c>
+      <c r="M280" s="4"/>
       <c r="N280" s="3">
         <v>2</v>
       </c>
       <c r="O280" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="P280" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="Q280" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="R280" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="S280" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="R280" s="5"/>
+      <c r="S280" s="5"/>
       <c r="T280" s="3" t="s">
         <v>130</v>
       </c>
@@ -19526,19 +19532,19 @@
         <v>12431</v>
       </c>
       <c r="B281" s="3">
-        <v>690678</v>
+        <v>692472</v>
       </c>
       <c r="C281" s="3">
-        <v>3682</v>
+        <v>3653</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="G281" s="3" t="s">
         <v>130</v>
@@ -19547,38 +19553,32 @@
         <v>6</v>
       </c>
       <c r="I281" s="3" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="J281" s="3">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K281" s="3" t="s">
-        <v>57</v>
+        <v>913</v>
       </c>
       <c r="L281" s="3" t="s">
-        <v>902</v>
-      </c>
-      <c r="M281" s="10" t="s">
-        <v>784</v>
-      </c>
+        <v>914</v>
+      </c>
+      <c r="M281" s="4"/>
       <c r="N281" s="3">
         <v>2</v>
       </c>
       <c r="O281" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="P281" s="3" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="Q281" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="R281" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="S281" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="R281" s="5"/>
+      <c r="S281" s="5"/>
       <c r="T281" s="3" t="s">
         <v>130</v>
       </c>
@@ -19588,57 +19588,57 @@
         <v>12431</v>
       </c>
       <c r="B282" s="3">
-        <v>692607</v>
+        <v>692477</v>
       </c>
       <c r="C282" s="3">
-        <v>6364</v>
+        <v>2629</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F282" s="3" t="s">
-        <v>905</v>
+        <v>21</v>
+      </c>
+      <c r="F282" s="3">
+        <v>653521795</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="H282" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I282" s="3" t="s">
-        <v>906</v>
+        <v>916</v>
       </c>
       <c r="J282" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K282" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L282" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="M282" s="10" t="s">
-        <v>784</v>
-      </c>
+        <v>917</v>
+      </c>
+      <c r="L282" s="5"/>
+      <c r="M282" s="6"/>
       <c r="N282" s="3">
         <v>1</v>
       </c>
       <c r="O282" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="P282" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="Q282" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R282" s="5"/>
-      <c r="S282" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="R282" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="S282" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="T282" s="3" t="s">
-        <v>294</v>
+        <v>109</v>
       </c>
     </row>
     <row r="283" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19646,55 +19646,57 @@
         <v>12431</v>
       </c>
       <c r="B283" s="3">
-        <v>692471</v>
+        <v>681280</v>
       </c>
       <c r="C283" s="3">
-        <v>3653</v>
+        <v>6466</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>908</v>
+        <v>918</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>909</v>
+        <v>919</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="H283" s="3">
         <v>6</v>
       </c>
       <c r="I283" s="3" t="s">
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="J283" s="3">
+        <v>18</v>
+      </c>
+      <c r="K283" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L283" s="5"/>
+      <c r="M283" s="6"/>
+      <c r="N283" s="3">
+        <v>1</v>
+      </c>
+      <c r="O283" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="P283" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K283" s="3" t="s">
-        <v>911</v>
-      </c>
-      <c r="L283" s="3" t="s">
-        <v>912</v>
-      </c>
-      <c r="M283" s="4"/>
-      <c r="N283" s="3">
-        <v>2</v>
-      </c>
-      <c r="O283" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="P283" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="Q283" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="R283" s="5"/>
-      <c r="S283" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="R283" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S283" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="T283" s="3" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
     </row>
     <row r="284" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19702,55 +19704,55 @@
         <v>12431</v>
       </c>
       <c r="B284" s="3">
-        <v>692472</v>
+        <v>692533</v>
       </c>
       <c r="C284" s="3">
-        <v>3653</v>
+        <v>6517</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="H284" s="3">
         <v>6</v>
       </c>
       <c r="I284" s="3" t="s">
-        <v>913</v>
+        <v>923</v>
       </c>
       <c r="J284" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K284" s="3" t="s">
-        <v>914</v>
+        <v>142</v>
       </c>
       <c r="L284" s="3" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="M284" s="4"/>
       <c r="N284" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O284" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P284" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q284" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="Q284" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="R284" s="5"/>
       <c r="S284" s="5"/>
       <c r="T284" s="3" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
     </row>
     <row r="285" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19758,57 +19760,59 @@
         <v>12431</v>
       </c>
       <c r="B285" s="3">
-        <v>692477</v>
+        <v>692629</v>
       </c>
       <c r="C285" s="3">
-        <v>2629</v>
+        <v>9265</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F285" s="3">
-        <v>653521795</v>
+        <v>31</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>926</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="H285" s="3">
         <v>6</v>
       </c>
       <c r="I285" s="3" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="J285" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="K285" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="L285" s="5"/>
-      <c r="M285" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="L285" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="M285" s="4"/>
       <c r="N285" s="3">
         <v>1</v>
       </c>
       <c r="O285" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="P285" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="P285" s="3" t="s">
+      <c r="Q285" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R285" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S285" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Q285" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="R285" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="S285" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="T285" s="3" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
     </row>
     <row r="286" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19816,57 +19820,57 @@
         <v>12431</v>
       </c>
       <c r="B286" s="3">
-        <v>681280</v>
+        <v>692498</v>
       </c>
       <c r="C286" s="3">
-        <v>6466</v>
+        <v>6427</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="H286" s="3">
         <v>6</v>
       </c>
       <c r="I286" s="3" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="J286" s="3">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K286" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L286" s="5"/>
       <c r="M286" s="6"/>
       <c r="N286" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O286" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="P286" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q286" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R286" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S286" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="Q286" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R286" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S286" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="T286" s="3" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
     </row>
     <row r="287" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -19874,173 +19878,159 @@
         <v>12431</v>
       </c>
       <c r="B287" s="3">
-        <v>692533</v>
+        <v>692499</v>
       </c>
       <c r="C287" s="3">
-        <v>6517</v>
+        <v>6427</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="H287" s="3">
         <v>6</v>
       </c>
       <c r="I287" s="3" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="J287" s="3">
+        <v>28</v>
+      </c>
+      <c r="K287" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L287" s="5"/>
+      <c r="M287" s="6"/>
+      <c r="N287" s="3">
+        <v>2</v>
+      </c>
+      <c r="O287" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P287" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q287" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R287" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S287" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K287" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="L287" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="M287" s="4"/>
-      <c r="N287" s="3">
+      <c r="T287" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="288" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+      <c r="A288" s="3">
+        <v>12431</v>
+      </c>
+      <c r="B288" s="3">
+        <v>692656</v>
+      </c>
+      <c r="C288" s="3">
+        <v>3644</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H288" s="3">
         <v>1</v>
       </c>
-      <c r="O287" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="P287" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q287" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="R287" s="5"/>
-      <c r="S287" s="5"/>
-      <c r="T287" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="288" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A288" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B288" s="3">
-        <v>692629</v>
-      </c>
-      <c r="C288" s="3">
-        <v>9265</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="E288" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F288" s="3" t="s">
-        <v>927</v>
-      </c>
-      <c r="G288" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H288" s="3">
-        <v>6</v>
-      </c>
       <c r="I288" s="3" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="J288" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K288" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L288" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="M288" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="L288" s="7" t="s">
+        <v>936</v>
+      </c>
+      <c r="M288" s="11" t="s">
+        <v>783</v>
+      </c>
       <c r="N288" s="3">
         <v>1</v>
       </c>
       <c r="O288" s="3" t="s">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="P288" s="3" t="s">
         <v>47</v>
       </c>
       <c r="Q288" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R288" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S288" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="R288" s="5"/>
+      <c r="S288" s="5"/>
       <c r="T288" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="289" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A289" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B289" s="3">
-        <v>692498</v>
-      </c>
-      <c r="C289" s="3">
-        <v>6427</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>930</v>
-      </c>
-      <c r="E289" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A289">
+        <v>12431</v>
+      </c>
+      <c r="B289">
+        <v>693455</v>
+      </c>
+      <c r="C289">
+        <v>5492</v>
+      </c>
+      <c r="D289" t="s">
+        <v>937</v>
+      </c>
+      <c r="E289" t="s">
         <v>21</v>
       </c>
-      <c r="F289" s="3" t="s">
-        <v>931</v>
-      </c>
-      <c r="G289" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H289" s="3">
-        <v>6</v>
-      </c>
-      <c r="I289" s="3" t="s">
-        <v>932</v>
-      </c>
-      <c r="J289" s="3">
-        <v>29</v>
-      </c>
-      <c r="K289" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L289" s="5"/>
-      <c r="M289" s="6"/>
-      <c r="N289" s="3">
-        <v>2</v>
-      </c>
-      <c r="O289" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P289" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q289" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R289" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="S289" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="T289" s="3" t="s">
-        <v>85</v>
+      <c r="F289" t="s">
+        <v>938</v>
+      </c>
+      <c r="G289" t="s">
+        <v>140</v>
+      </c>
+      <c r="H289">
+        <v>6</v>
+      </c>
+      <c r="I289" t="s">
+        <v>939</v>
+      </c>
+      <c r="J289">
+        <v>10</v>
+      </c>
+      <c r="M289" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="N289">
+        <v>1</v>
+      </c>
+      <c r="O289" t="s">
+        <v>940</v>
+      </c>
+      <c r="T289" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="290" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -20048,226 +20038,78 @@
         <v>12431</v>
       </c>
       <c r="B290" s="3">
-        <v>692499</v>
+        <v>692888</v>
       </c>
       <c r="C290" s="3">
-        <v>6427</v>
+        <v>6512</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="E290" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F290" s="3" t="s">
-        <v>931</v>
-      </c>
       <c r="G290" s="3" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="H290" s="3">
         <v>6</v>
       </c>
       <c r="I290" s="3" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="J290" s="3">
-        <v>28</v>
-      </c>
-      <c r="K290" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L290" s="5"/>
-      <c r="M290" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="M290" s="1"/>
       <c r="N290" s="3">
         <v>2</v>
       </c>
-      <c r="O290" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P290" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q290" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R290" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="S290" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="T290" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="291" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="291" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A291" s="3">
         <v>12431</v>
       </c>
       <c r="B291" s="3">
-        <v>692656</v>
+        <v>692889</v>
       </c>
       <c r="C291" s="3">
-        <v>3644</v>
+        <v>6512</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F291" s="3" t="s">
-        <v>935</v>
-      </c>
       <c r="G291" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H291" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I291" s="3" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="J291" s="3">
-        <v>9</v>
-      </c>
-      <c r="K291" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L291" s="7" t="s">
-        <v>937</v>
-      </c>
-      <c r="M291" s="11" t="s">
-        <v>784</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="M291" s="1"/>
       <c r="N291" s="3">
-        <v>1</v>
-      </c>
-      <c r="O291" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P291" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q291" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R291" s="5"/>
-      <c r="S291" s="5"/>
-      <c r="T291" s="3" t="s">
-        <v>130</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A292">
-        <v>12431</v>
-      </c>
-      <c r="B292">
-        <v>693455</v>
-      </c>
-      <c r="C292">
-        <v>5492</v>
-      </c>
-      <c r="D292" t="s">
-        <v>938</v>
-      </c>
-      <c r="E292" t="s">
-        <v>21</v>
-      </c>
-      <c r="F292" t="s">
-        <v>939</v>
-      </c>
-      <c r="G292" t="s">
-        <v>140</v>
-      </c>
-      <c r="H292">
-        <v>6</v>
-      </c>
-      <c r="I292" t="s">
-        <v>940</v>
-      </c>
-      <c r="J292">
-        <v>10</v>
-      </c>
-      <c r="M292" s="12" t="s">
-        <v>827</v>
-      </c>
-      <c r="N292">
-        <v>1</v>
-      </c>
-      <c r="O292" t="s">
-        <v>941</v>
-      </c>
-      <c r="T292" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="293" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A293" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B293" s="3">
-        <v>692888</v>
-      </c>
-      <c r="C293" s="3">
-        <v>6512</v>
-      </c>
-      <c r="D293" s="3" t="s">
-        <v>942</v>
-      </c>
-      <c r="E293" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G293" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H293" s="3">
-        <v>6</v>
-      </c>
-      <c r="I293" s="3" t="s">
-        <v>943</v>
-      </c>
-      <c r="J293" s="3">
-        <v>17</v>
-      </c>
-      <c r="M293" s="1"/>
-      <c r="N293" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="294" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A294" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B294" s="3">
-        <v>692889</v>
-      </c>
-      <c r="C294" s="3">
-        <v>6512</v>
-      </c>
-      <c r="D294" s="3" t="s">
-        <v>942</v>
-      </c>
-      <c r="E294" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G294" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H294" s="3">
-        <v>6</v>
-      </c>
-      <c r="I294" s="3" t="s">
-        <v>944</v>
-      </c>
-      <c r="J294" s="3">
-        <v>18</v>
-      </c>
-      <c r="M294" s="1"/>
-      <c r="N294" s="3">
-        <v>2</v>
-      </c>
+      <c r="L292" s="13"/>
+      <c r="M292" s="14"/>
+    </row>
+    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="L293" s="13"/>
+      <c r="M293" s="14"/>
+    </row>
+    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="L294" s="13"/>
+      <c r="M294" s="14"/>
     </row>
     <row r="295" spans="1:20" x14ac:dyDescent="0.35">
       <c r="L295" s="13"/>
@@ -20305,42 +20147,30 @@
       <c r="L303" s="13"/>
       <c r="M303" s="14"/>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L304" s="13"/>
-      <c r="M304" s="14"/>
-    </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L305" s="13"/>
-      <c r="M305" s="14"/>
-    </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L306" s="13"/>
-      <c r="M306" s="14"/>
-    </row>
-    <row r="307" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A307" s="15"/>
-      <c r="B307" s="16"/>
-      <c r="C307" s="17"/>
-      <c r="D307" s="18"/>
-      <c r="E307" s="19"/>
-      <c r="F307" s="15"/>
-      <c r="G307" s="15"/>
-      <c r="H307" s="15"/>
-      <c r="I307" s="20"/>
-      <c r="J307" s="21"/>
-      <c r="K307" s="15"/>
-      <c r="L307" s="22"/>
-      <c r="M307" s="23"/>
-      <c r="N307" s="15"/>
-      <c r="O307" s="15"/>
-      <c r="P307" s="15"/>
-      <c r="Q307" s="15"/>
-      <c r="R307" s="15"/>
-      <c r="S307" s="15"/>
-      <c r="T307" s="15"/>
+    <row r="304" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A304" s="15"/>
+      <c r="B304" s="16"/>
+      <c r="C304" s="17"/>
+      <c r="D304" s="18"/>
+      <c r="E304" s="19"/>
+      <c r="F304" s="15"/>
+      <c r="G304" s="15"/>
+      <c r="H304" s="15"/>
+      <c r="I304" s="20"/>
+      <c r="J304" s="21"/>
+      <c r="K304" s="15"/>
+      <c r="L304" s="22"/>
+      <c r="M304" s="23"/>
+      <c r="N304" s="15"/>
+      <c r="O304" s="15"/>
+      <c r="P304" s="15"/>
+      <c r="Q304" s="15"/>
+      <c r="R304" s="15"/>
+      <c r="S304" s="15"/>
+      <c r="T304" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M1:M307">
+  <conditionalFormatting sqref="M1:M304">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"ENGELS"</formula>
     </cfRule>

--- a/data/SCHOOLS 2025.xlsx
+++ b/data/SCHOOLS 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FlorisKuipersADC\Python_Projects\Schooltuinen%20Amsterdam\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63A7533-F734-40E2-895E-5297A22200F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571AFF4C-C565-464A-8E44-36D17584B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5753D62C-6060-44DC-AE8B-171BC587F40A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3392" uniqueCount="941">
   <si>
     <t>code</t>
   </si>
@@ -2887,15 +2887,6 @@
   </si>
   <si>
     <t>woensdag 9:00-10:30 uur</t>
-  </si>
-  <si>
-    <t>Rosj Pina</t>
-  </si>
-  <si>
-    <t>6A</t>
-  </si>
-  <si>
-    <t>6B</t>
   </si>
 </sst>
 </file>
@@ -20034,70 +20025,30 @@
       </c>
     </row>
     <row r="290" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A290" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B290" s="3">
-        <v>692888</v>
-      </c>
-      <c r="C290" s="3">
-        <v>6512</v>
-      </c>
-      <c r="D290" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="E290" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G290" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H290" s="3">
-        <v>6</v>
-      </c>
-      <c r="I290" s="3" t="s">
-        <v>942</v>
-      </c>
-      <c r="J290" s="3">
-        <v>17</v>
-      </c>
+      <c r="A290" s="3"/>
+      <c r="B290" s="3"/>
+      <c r="C290" s="3"/>
+      <c r="D290" s="3"/>
+      <c r="E290" s="3"/>
+      <c r="G290" s="3"/>
+      <c r="H290" s="3"/>
+      <c r="I290" s="3"/>
+      <c r="J290" s="3"/>
       <c r="M290" s="1"/>
-      <c r="N290" s="3">
-        <v>2</v>
-      </c>
+      <c r="N290" s="3"/>
     </row>
     <row r="291" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A291" s="3">
-        <v>12431</v>
-      </c>
-      <c r="B291" s="3">
-        <v>692889</v>
-      </c>
-      <c r="C291" s="3">
-        <v>6512</v>
-      </c>
-      <c r="D291" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="E291" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G291" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H291" s="3">
-        <v>6</v>
-      </c>
-      <c r="I291" s="3" t="s">
-        <v>943</v>
-      </c>
-      <c r="J291" s="3">
-        <v>18</v>
-      </c>
+      <c r="A291" s="3"/>
+      <c r="B291" s="3"/>
+      <c r="C291" s="3"/>
+      <c r="D291" s="3"/>
+      <c r="E291" s="3"/>
+      <c r="G291" s="3"/>
+      <c r="H291" s="3"/>
+      <c r="I291" s="3"/>
+      <c r="J291" s="3"/>
       <c r="M291" s="1"/>
-      <c r="N291" s="3">
-        <v>2</v>
-      </c>
+      <c r="N291" s="3"/>
     </row>
     <row r="292" spans="1:20" x14ac:dyDescent="0.35">
       <c r="L292" s="13"/>

--- a/data/SCHOOLS 2025.xlsx
+++ b/data/SCHOOLS 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FlorisKuipersADC\Python_Projects\Schooltuinen%20Amsterdam\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsterdamdatacollective-my.sharepoint.com/personal/thomas_b_adc-consulting_com/Documents/Documents/Collective Week/Code/Schooltuinen%20Amsterdam/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571AFF4C-C565-464A-8E44-36D17584B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{571AFF4C-C565-464A-8E44-36D17584B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEED746B-65A0-4DCB-9E9C-1204687A3D0C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5753D62C-6060-44DC-AE8B-171BC587F40A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5753D62C-6060-44DC-AE8B-171BC587F40A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3081,6 +3081,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3401,16 +3405,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43430540-BBA7-4347-B81D-8C67916B1A6D}">
   <dimension ref="A1:T304"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" customWidth="1"/>
+    <col min="4" max="4" width="47.88671875" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.36328125" customWidth="1"/>
+    <col min="7" max="7" width="41" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="77.88671875" customWidth="1"/>
+    <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3472,7 +3481,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>12431</v>
       </c>
@@ -3528,7 +3537,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>12431</v>
       </c>
@@ -3582,7 +3591,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>12431</v>
       </c>
@@ -3638,7 +3647,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>12431</v>
       </c>
@@ -3696,7 +3705,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>12431</v>
       </c>
@@ -3754,7 +3763,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>12431</v>
       </c>
@@ -3812,7 +3821,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>12431</v>
       </c>
@@ -3870,7 +3879,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>12431</v>
       </c>
@@ -3930,7 +3939,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>12431</v>
       </c>
@@ -3986,7 +3995,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>12431</v>
       </c>
@@ -4042,7 +4051,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>12431</v>
       </c>
@@ -4100,7 +4109,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12431</v>
       </c>
@@ -4156,7 +4165,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>12431</v>
       </c>
@@ -4212,7 +4221,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12431</v>
       </c>
@@ -4268,7 +4277,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>12431</v>
       </c>
@@ -4324,7 +4333,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>12431</v>
       </c>
@@ -4382,7 +4391,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>12431</v>
       </c>
@@ -4438,7 +4447,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>12431</v>
       </c>
@@ -4494,7 +4503,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>12431</v>
       </c>
@@ -4548,7 +4557,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>12431</v>
       </c>
@@ -4606,7 +4615,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>12431</v>
       </c>
@@ -4666,7 +4675,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>12431</v>
       </c>
@@ -4726,7 +4735,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>12431</v>
       </c>
@@ -4782,7 +4791,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>12431</v>
       </c>
@@ -4838,7 +4847,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>12431</v>
       </c>
@@ -4894,7 +4903,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>12431</v>
       </c>
@@ -4950,7 +4959,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>12431</v>
       </c>
@@ -5006,7 +5015,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="225.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" ht="243" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>12431</v>
       </c>
@@ -5064,7 +5073,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="225.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" ht="243" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>12431</v>
       </c>
@@ -5122,7 +5131,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="225.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" ht="243" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>12431</v>
       </c>
@@ -5180,7 +5189,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="225.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" ht="243" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>12431</v>
       </c>
@@ -5238,7 +5247,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>12431</v>
       </c>
@@ -5296,7 +5305,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>12431</v>
       </c>
@@ -5354,7 +5363,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>12431</v>
       </c>
@@ -5412,7 +5421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>12431</v>
       </c>
@@ -5472,7 +5481,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>12431</v>
       </c>
@@ -5532,7 +5541,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>12431</v>
       </c>
@@ -5588,7 +5597,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>12431</v>
       </c>
@@ -5644,7 +5653,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>12431</v>
       </c>
@@ -5700,7 +5709,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>12431</v>
       </c>
@@ -5756,7 +5765,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>12431</v>
       </c>
@@ -5806,7 +5815,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>12431</v>
       </c>
@@ -5866,7 +5875,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>12431</v>
       </c>
@@ -5924,7 +5933,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>12431</v>
       </c>
@@ -5982,7 +5991,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>12431</v>
       </c>
@@ -6040,7 +6049,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>12431</v>
       </c>
@@ -6096,7 +6105,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>12431</v>
       </c>
@@ -6156,7 +6165,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>12431</v>
       </c>
@@ -6216,7 +6225,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>12431</v>
       </c>
@@ -6272,7 +6281,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>12431</v>
       </c>
@@ -6328,7 +6337,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>12431</v>
       </c>
@@ -6384,7 +6393,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>12431</v>
       </c>
@@ -6440,7 +6449,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>12431</v>
       </c>
@@ -6496,7 +6505,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>12431</v>
       </c>
@@ -6556,7 +6565,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>12431</v>
       </c>
@@ -6616,7 +6625,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>12431</v>
       </c>
@@ -6672,7 +6681,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>12431</v>
       </c>
@@ -6728,7 +6737,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>12431</v>
       </c>
@@ -6788,7 +6797,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>12431</v>
       </c>
@@ -6848,7 +6857,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>12431</v>
       </c>
@@ -6904,7 +6913,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>12431</v>
       </c>
@@ -6960,7 +6969,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>12431</v>
       </c>
@@ -7016,7 +7025,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>12431</v>
       </c>
@@ -7072,7 +7081,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>12431</v>
       </c>
@@ -7132,7 +7141,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>12431</v>
       </c>
@@ -7192,7 +7201,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>12431</v>
       </c>
@@ -7252,7 +7261,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>12431</v>
       </c>
@@ -7312,7 +7321,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>12431</v>
       </c>
@@ -7368,7 +7377,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>12431</v>
       </c>
@@ -7428,7 +7437,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>12431</v>
       </c>
@@ -7488,7 +7497,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>12431</v>
       </c>
@@ -7548,7 +7557,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>12431</v>
       </c>
@@ -7608,7 +7617,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>12431</v>
       </c>
@@ -7668,7 +7677,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>12431</v>
       </c>
@@ -7728,7 +7737,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>12431</v>
       </c>
@@ -7784,7 +7793,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>12431</v>
       </c>
@@ -7840,7 +7849,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>12431</v>
       </c>
@@ -7896,7 +7905,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>12431</v>
       </c>
@@ -7956,7 +7965,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>12431</v>
       </c>
@@ -8016,7 +8025,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>12431</v>
       </c>
@@ -8076,7 +8085,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>12431</v>
       </c>
@@ -8134,7 +8143,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>12431</v>
       </c>
@@ -8194,7 +8203,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>12431</v>
       </c>
@@ -8250,7 +8259,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>12431</v>
       </c>
@@ -8306,7 +8315,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>12431</v>
       </c>
@@ -8364,7 +8373,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>12431</v>
       </c>
@@ -8424,7 +8433,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>12431</v>
       </c>
@@ -8484,7 +8493,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>12431</v>
       </c>
@@ -8544,7 +8553,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>12431</v>
       </c>
@@ -8604,7 +8613,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>12431</v>
       </c>
@@ -8660,7 +8669,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>12431</v>
       </c>
@@ -8716,7 +8725,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>12431</v>
       </c>
@@ -8772,7 +8781,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>12431</v>
       </c>
@@ -8828,7 +8837,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>12431</v>
       </c>
@@ -8884,7 +8893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>12431</v>
       </c>
@@ -8940,7 +8949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>12431</v>
       </c>
@@ -8996,7 +9005,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>12431</v>
       </c>
@@ -9052,7 +9061,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>12431</v>
       </c>
@@ -9112,7 +9121,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>12431</v>
       </c>
@@ -9168,7 +9177,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>12431</v>
       </c>
@@ -9224,7 +9233,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>12431</v>
       </c>
@@ -9284,7 +9293,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>12431</v>
       </c>
@@ -9340,7 +9349,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>12431</v>
       </c>
@@ -9398,7 +9407,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>12431</v>
       </c>
@@ -9456,7 +9465,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>12431</v>
       </c>
@@ -9512,7 +9521,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>12431</v>
       </c>
@@ -9568,7 +9577,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>12431</v>
       </c>
@@ -9626,7 +9635,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>12431</v>
       </c>
@@ -9684,7 +9693,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>12431</v>
       </c>
@@ -9740,7 +9749,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>12431</v>
       </c>
@@ -9800,7 +9809,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>12431</v>
       </c>
@@ -9858,7 +9867,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>12431</v>
       </c>
@@ -9916,7 +9925,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>12431</v>
       </c>
@@ -9970,7 +9979,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>12431</v>
       </c>
@@ -10024,7 +10033,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>12431</v>
       </c>
@@ -10080,7 +10089,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>12431</v>
       </c>
@@ -10134,7 +10143,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>12431</v>
       </c>
@@ -10190,7 +10199,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>12431</v>
       </c>
@@ -10246,7 +10255,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>12431</v>
       </c>
@@ -10300,7 +10309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>12431</v>
       </c>
@@ -10356,7 +10365,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>12431</v>
       </c>
@@ -10412,7 +10421,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>12431</v>
       </c>
@@ -10468,7 +10477,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>12431</v>
       </c>
@@ -10524,7 +10533,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>12431</v>
       </c>
@@ -10580,7 +10589,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>12431</v>
       </c>
@@ -10640,7 +10649,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>12431</v>
       </c>
@@ -10698,7 +10707,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>12431</v>
       </c>
@@ -10754,7 +10763,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>12431</v>
       </c>
@@ -10810,7 +10819,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>12431</v>
       </c>
@@ -10864,7 +10873,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>12431</v>
       </c>
@@ -10918,7 +10927,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>12431</v>
       </c>
@@ -10978,7 +10987,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>12431</v>
       </c>
@@ -11036,7 +11045,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>12431</v>
       </c>
@@ -11094,7 +11103,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>12431</v>
       </c>
@@ -11154,7 +11163,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>12431</v>
       </c>
@@ -11214,7 +11223,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>12431</v>
       </c>
@@ -11274,7 +11283,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>12431</v>
       </c>
@@ -11330,7 +11339,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>12431</v>
       </c>
@@ -11386,7 +11395,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>12431</v>
       </c>
@@ -11444,7 +11453,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>12431</v>
       </c>
@@ -11500,7 +11509,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>12431</v>
       </c>
@@ -11560,7 +11569,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>12431</v>
       </c>
@@ -11618,7 +11627,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>12431</v>
       </c>
@@ -11678,7 +11687,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>12431</v>
       </c>
@@ -11736,7 +11745,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>12431</v>
       </c>
@@ -11796,7 +11805,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>12431</v>
       </c>
@@ -11856,7 +11865,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>12431</v>
       </c>
@@ -11916,7 +11925,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>12431</v>
       </c>
@@ -11972,7 +11981,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>12431</v>
       </c>
@@ -12028,7 +12037,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>12431</v>
       </c>
@@ -12088,7 +12097,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>12431</v>
       </c>
@@ -12148,7 +12157,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>12431</v>
       </c>
@@ -12208,7 +12217,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>12431</v>
       </c>
@@ -12266,7 +12275,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>12431</v>
       </c>
@@ -12324,7 +12333,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>12431</v>
       </c>
@@ -12380,7 +12389,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>12431</v>
       </c>
@@ -12436,7 +12445,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>12431</v>
       </c>
@@ -12494,7 +12503,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>12431</v>
       </c>
@@ -12552,7 +12561,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>12431</v>
       </c>
@@ -12612,7 +12621,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>12431</v>
       </c>
@@ -12672,7 +12681,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>12431</v>
       </c>
@@ -12726,7 +12735,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>12431</v>
       </c>
@@ -12780,7 +12789,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>12431</v>
       </c>
@@ -12838,7 +12847,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>12431</v>
       </c>
@@ -12896,7 +12905,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>12431</v>
       </c>
@@ -12954,7 +12963,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>12431</v>
       </c>
@@ -13010,7 +13019,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>12431</v>
       </c>
@@ -13066,7 +13075,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>12431</v>
       </c>
@@ -13122,7 +13131,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>12431</v>
       </c>
@@ -13178,7 +13187,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>12431</v>
       </c>
@@ -13234,7 +13243,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>12431</v>
       </c>
@@ -13294,7 +13303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>12431</v>
       </c>
@@ -13354,7 +13363,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>12431</v>
       </c>
@@ -13414,7 +13423,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>12431</v>
       </c>
@@ -13470,7 +13479,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>12431</v>
       </c>
@@ -13530,7 +13539,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>12431</v>
       </c>
@@ -13584,7 +13593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>12431</v>
       </c>
@@ -13640,7 +13649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>12431</v>
       </c>
@@ -13696,7 +13705,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>12431</v>
       </c>
@@ -13752,7 +13761,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>12431</v>
       </c>
@@ -13808,7 +13817,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="182" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>12431</v>
       </c>
@@ -13866,7 +13875,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="183" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>12431</v>
       </c>
@@ -13926,7 +13935,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>12431</v>
       </c>
@@ -13984,7 +13993,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="185" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>12431</v>
       </c>
@@ -14040,7 +14049,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>12431</v>
       </c>
@@ -14096,7 +14105,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="187" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>12431</v>
       </c>
@@ -14152,7 +14161,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="188" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>12431</v>
       </c>
@@ -14208,7 +14217,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="189" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>12431</v>
       </c>
@@ -14262,7 +14271,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="190" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>12431</v>
       </c>
@@ -14322,7 +14331,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="191" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>12431</v>
       </c>
@@ -14378,7 +14387,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="192" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>12431</v>
       </c>
@@ -14434,7 +14443,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="193" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>12431</v>
       </c>
@@ -14488,7 +14497,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>12431</v>
       </c>
@@ -14542,7 +14551,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>12431</v>
       </c>
@@ -14600,7 +14609,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="196" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>12431</v>
       </c>
@@ -14660,7 +14669,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="197" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>12431</v>
       </c>
@@ -14716,7 +14725,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="198" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>12431</v>
       </c>
@@ -14772,7 +14781,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:20" ht="210.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:20" ht="226.8" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>12431</v>
       </c>
@@ -14828,7 +14837,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>12431</v>
       </c>
@@ -14884,7 +14893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>12431</v>
       </c>
@@ -14940,7 +14949,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>12431</v>
       </c>
@@ -15000,7 +15009,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="203" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>12431</v>
       </c>
@@ -15060,7 +15069,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>12431</v>
       </c>
@@ -15110,7 +15119,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="205" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>12431</v>
       </c>
@@ -15160,7 +15169,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="206" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>12431</v>
       </c>
@@ -15210,7 +15219,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="207" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>12431</v>
       </c>
@@ -15270,7 +15279,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="208" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>12431</v>
       </c>
@@ -15330,7 +15339,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="209" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>12431</v>
       </c>
@@ -15390,7 +15399,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="210" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>12431</v>
       </c>
@@ -15446,7 +15455,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="211" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>12431</v>
       </c>
@@ -15502,7 +15511,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>12431</v>
       </c>
@@ -15562,7 +15571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>12431</v>
       </c>
@@ -15616,7 +15625,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="214" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>12431</v>
       </c>
@@ -15670,7 +15679,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="215" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>12431</v>
       </c>
@@ -15726,7 +15735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>12431</v>
       </c>
@@ -15782,7 +15791,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="217" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>12431</v>
       </c>
@@ -15838,7 +15847,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="218" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>12431</v>
       </c>
@@ -15894,7 +15903,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="219" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>12431</v>
       </c>
@@ -15952,7 +15961,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="220" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>12431</v>
       </c>
@@ -16012,7 +16021,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="221" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>12431</v>
       </c>
@@ -16072,7 +16081,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="222" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>12431</v>
       </c>
@@ -16128,7 +16137,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="223" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>12431</v>
       </c>
@@ -16184,7 +16193,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="224" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>12431</v>
       </c>
@@ -16240,7 +16249,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="225" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>12431</v>
       </c>
@@ -16296,7 +16305,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="226" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>12431</v>
       </c>
@@ -16352,7 +16361,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="227" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>12431</v>
       </c>
@@ -16410,7 +16419,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="228" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>12431</v>
       </c>
@@ -16470,7 +16479,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="229" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>12431</v>
       </c>
@@ -16528,7 +16537,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="230" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>12431</v>
       </c>
@@ -16586,7 +16595,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="231" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>12431</v>
       </c>
@@ -16644,7 +16653,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="232" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>12431</v>
       </c>
@@ -16700,7 +16709,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="233" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>12431</v>
       </c>
@@ -16758,7 +16767,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="234" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>12431</v>
       </c>
@@ -16814,7 +16823,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="235" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>12431</v>
       </c>
@@ -16870,7 +16879,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="236" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>12431</v>
       </c>
@@ -16930,7 +16939,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="237" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>12431</v>
       </c>
@@ -16992,7 +17001,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="238" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>12431</v>
       </c>
@@ -17054,7 +17063,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="239" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>12431</v>
       </c>
@@ -17110,7 +17119,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="240" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>12431</v>
       </c>
@@ -17166,7 +17175,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="241" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>12431</v>
       </c>
@@ -17222,7 +17231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>12431</v>
       </c>
@@ -17278,7 +17287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="243" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>12431</v>
       </c>
@@ -17336,7 +17345,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="244" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>12431</v>
       </c>
@@ -17394,7 +17403,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="245" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>12431</v>
       </c>
@@ -17452,7 +17461,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>12431</v>
       </c>
@@ -17514,7 +17523,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="247" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>12431</v>
       </c>
@@ -17576,7 +17585,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="248" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>12431</v>
       </c>
@@ -17634,7 +17643,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="249" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>12431</v>
       </c>
@@ -17692,7 +17701,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="250" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>12431</v>
       </c>
@@ -17750,7 +17759,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>12431</v>
       </c>
@@ -17808,7 +17817,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>12431</v>
       </c>
@@ -17866,7 +17875,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="253" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>12431</v>
       </c>
@@ -17924,7 +17933,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="254" spans="1:20" ht="180.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:20" ht="210.6" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>12431</v>
       </c>
@@ -17986,7 +17995,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="255" spans="1:20" ht="165.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:20" ht="194.4" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>12431</v>
       </c>
@@ -18048,7 +18057,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="256" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>12431</v>
       </c>
@@ -18106,7 +18115,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="257" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>12431</v>
       </c>
@@ -18168,7 +18177,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="258" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>12431</v>
       </c>
@@ -18230,7 +18239,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="259" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>12431</v>
       </c>
@@ -18286,7 +18295,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="260" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>12431</v>
       </c>
@@ -18346,7 +18355,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="261" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>12431</v>
       </c>
@@ -18400,7 +18409,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="262" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>12431</v>
       </c>
@@ -18456,7 +18465,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="263" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>12431</v>
       </c>
@@ -18516,7 +18525,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="264" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>12431</v>
       </c>
@@ -18576,7 +18585,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="265" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>12431</v>
       </c>
@@ -18636,7 +18645,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="266" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>12431</v>
       </c>
@@ -18696,7 +18705,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="267" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>12431</v>
       </c>
@@ -18750,7 +18759,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="268" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>12431</v>
       </c>
@@ -18810,7 +18819,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="269" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>12431</v>
       </c>
@@ -18868,7 +18877,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="270" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>12431</v>
       </c>
@@ -18928,7 +18937,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="271" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>12431</v>
       </c>
@@ -18988,7 +18997,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="272" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>12431</v>
       </c>
@@ -19048,7 +19057,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="273" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>12431</v>
       </c>
@@ -19108,7 +19117,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="274" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>12431</v>
       </c>
@@ -19164,7 +19173,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="275" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>12431</v>
       </c>
@@ -19220,7 +19229,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="276" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>12431</v>
       </c>
@@ -19280,7 +19289,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="277" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>12431</v>
       </c>
@@ -19342,7 +19351,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="278" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>12431</v>
       </c>
@@ -19404,7 +19413,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="279" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>12431</v>
       </c>
@@ -19462,7 +19471,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="280" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>12431</v>
       </c>
@@ -19518,7 +19527,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="281" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>12431</v>
       </c>
@@ -19574,7 +19583,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="282" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>12431</v>
       </c>
@@ -19632,7 +19641,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="283" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>12431</v>
       </c>
@@ -19690,7 +19699,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="284" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>12431</v>
       </c>
@@ -19746,7 +19755,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="285" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>12431</v>
       </c>
@@ -19806,7 +19815,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="286" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>12431</v>
       </c>
@@ -19864,7 +19873,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="287" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>12431</v>
       </c>
@@ -19922,7 +19931,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="288" spans="1:20" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>12431</v>
       </c>
@@ -19980,7 +19989,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>12431</v>
       </c>
@@ -20024,7 +20033,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -20037,7 +20046,7 @@
       <c r="M290" s="1"/>
       <c r="N290" s="3"/>
     </row>
-    <row r="291" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -20050,55 +20059,55 @@
       <c r="M291" s="1"/>
       <c r="N291" s="3"/>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L292" s="13"/>
       <c r="M292" s="14"/>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L293" s="13"/>
       <c r="M293" s="14"/>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L294" s="13"/>
       <c r="M294" s="14"/>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L295" s="13"/>
       <c r="M295" s="14"/>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L296" s="13"/>
       <c r="M296" s="14"/>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L297" s="13"/>
       <c r="M297" s="14"/>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L298" s="13"/>
       <c r="M298" s="14"/>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L299" s="13"/>
       <c r="M299" s="14"/>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L300" s="13"/>
       <c r="M300" s="14"/>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L301" s="13"/>
       <c r="M301" s="14"/>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L302" s="13"/>
       <c r="M302" s="14"/>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L303" s="13"/>
       <c r="M303" s="14"/>
     </row>
-    <row r="304" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A304" s="15"/>
       <c r="B304" s="16"/>
       <c r="C304" s="17"/>

--- a/data/SCHOOLS 2025.xlsx
+++ b/data/SCHOOLS 2025.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsterdamdatacollective-my.sharepoint.com/personal/thomas_b_adc-consulting_com/Documents/Documents/Collective Week/Code/Schooltuinen%20Amsterdam/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{571AFF4C-C565-464A-8E44-36D17584B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEED746B-65A0-4DCB-9E9C-1204687A3D0C}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{571AFF4C-C565-464A-8E44-36D17584B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DACFA45-1D1B-4A41-A8E1-DF2F08A5BF1E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5753D62C-6060-44DC-AE8B-171BC587F40A}"/>
+    <workbookView xWindow="0" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{5753D62C-6060-44DC-AE8B-171BC587F40A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$304</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3081,10 +3084,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3404,6 +3403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43430540-BBA7-4347-B81D-8C67916B1A6D}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:T304"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3415,6 +3415,8 @@
     <col min="7" max="7" width="41" customWidth="1"/>
     <col min="8" max="8" width="36" customWidth="1"/>
     <col min="9" max="9" width="77.88671875" customWidth="1"/>
+    <col min="11" max="11" width="97.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="255.77734375" customWidth="1"/>
     <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34.44140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -3481,7 +3483,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>12431</v>
       </c>
@@ -3523,13 +3525,13 @@
         <v>1</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5"/>
@@ -3537,7 +3539,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>12431</v>
       </c>
@@ -3591,7 +3593,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>12431</v>
       </c>
@@ -3647,7 +3649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>12431</v>
       </c>
@@ -3705,7 +3707,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>12431</v>
       </c>
@@ -3763,7 +3765,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>12431</v>
       </c>
@@ -3821,7 +3823,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>12431</v>
       </c>
@@ -3879,7 +3881,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>12431</v>
       </c>
@@ -3939,7 +3941,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>12431</v>
       </c>
@@ -3995,7 +3997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>12431</v>
       </c>
@@ -4051,7 +4053,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>12431</v>
       </c>
@@ -4109,7 +4111,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12431</v>
       </c>
@@ -4165,7 +4167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>12431</v>
       </c>
@@ -4221,7 +4223,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12431</v>
       </c>
@@ -4277,7 +4279,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="64.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>12431</v>
       </c>
@@ -4333,7 +4335,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>12431</v>
       </c>
@@ -4391,7 +4393,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="64.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>12431</v>
       </c>
@@ -4447,7 +4449,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="64.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>12431</v>
       </c>
@@ -4503,7 +4505,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>12431</v>
       </c>
@@ -4557,7 +4559,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>12431</v>
       </c>
@@ -4615,7 +4617,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>12431</v>
       </c>
@@ -4675,7 +4677,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>12431</v>
       </c>
@@ -4735,7 +4737,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>12431</v>
       </c>
@@ -5015,7 +5017,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="243" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>12431</v>
       </c>
@@ -5073,7 +5075,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="243" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>12431</v>
       </c>
@@ -5131,7 +5133,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="243" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>12431</v>
       </c>
@@ -5189,7 +5191,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="243" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>12431</v>
       </c>
@@ -5247,7 +5249,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>12431</v>
       </c>
@@ -5305,7 +5307,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>12431</v>
       </c>
@@ -5363,7 +5365,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>12431</v>
       </c>
@@ -5421,7 +5423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>12431</v>
       </c>
@@ -5481,7 +5483,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>12431</v>
       </c>
@@ -5541,7 +5543,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>12431</v>
       </c>
@@ -5597,7 +5599,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>12431</v>
       </c>
@@ -5653,7 +5655,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>12431</v>
       </c>
@@ -5709,7 +5711,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>12431</v>
       </c>
@@ -5765,7 +5767,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>12431</v>
       </c>
@@ -5815,7 +5817,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>12431</v>
       </c>
@@ -5875,7 +5877,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>12431</v>
       </c>
@@ -5933,7 +5935,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>12431</v>
       </c>
@@ -5991,7 +5993,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>12431</v>
       </c>
@@ -6049,7 +6051,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>12431</v>
       </c>
@@ -6105,7 +6107,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>12431</v>
       </c>
@@ -6165,7 +6167,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>12431</v>
       </c>
@@ -6225,7 +6227,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" ht="48.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>12431</v>
       </c>
@@ -6281,7 +6283,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" ht="48.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>12431</v>
       </c>
@@ -6337,7 +6339,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>12431</v>
       </c>
@@ -6393,7 +6395,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>12431</v>
       </c>
@@ -6449,7 +6451,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>12431</v>
       </c>
@@ -6505,7 +6507,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>12431</v>
       </c>
@@ -6565,7 +6567,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>12431</v>
       </c>
@@ -6625,7 +6627,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>12431</v>
       </c>
@@ -6681,7 +6683,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>12431</v>
       </c>
@@ -6737,7 +6739,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>12431</v>
       </c>
@@ -6797,7 +6799,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>12431</v>
       </c>
@@ -6913,7 +6915,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>12431</v>
       </c>
@@ -6969,7 +6971,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>12431</v>
       </c>
@@ -7025,7 +7027,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>12431</v>
       </c>
@@ -7081,7 +7083,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>12431</v>
       </c>
@@ -7141,7 +7143,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>12431</v>
       </c>
@@ -7201,7 +7203,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>12431</v>
       </c>
@@ -7261,7 +7263,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>12431</v>
       </c>
@@ -7321,7 +7323,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>12431</v>
       </c>
@@ -7377,7 +7379,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>12431</v>
       </c>
@@ -7437,7 +7439,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>12431</v>
       </c>
@@ -7497,7 +7499,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>12431</v>
       </c>
@@ -7557,7 +7559,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>12431</v>
       </c>
@@ -7617,7 +7619,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>12431</v>
       </c>
@@ -7677,7 +7679,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>12431</v>
       </c>
@@ -7737,7 +7739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>12431</v>
       </c>
@@ -7793,7 +7795,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>12431</v>
       </c>
@@ -7849,7 +7851,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>12431</v>
       </c>
@@ -7905,7 +7907,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>12431</v>
       </c>
@@ -7965,7 +7967,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>12431</v>
       </c>
@@ -8025,7 +8027,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>12431</v>
       </c>
@@ -8085,7 +8087,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>12431</v>
       </c>
@@ -8143,7 +8145,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>12431</v>
       </c>
@@ -8203,7 +8205,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>12431</v>
       </c>
@@ -8259,7 +8261,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>12431</v>
       </c>
@@ -8315,7 +8317,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>12431</v>
       </c>
@@ -8373,7 +8375,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" ht="48.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>12431</v>
       </c>
@@ -8433,7 +8435,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>12431</v>
       </c>
@@ -8493,7 +8495,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>12431</v>
       </c>
@@ -8553,7 +8555,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>12431</v>
       </c>
@@ -8613,7 +8615,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>12431</v>
       </c>
@@ -8669,7 +8671,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>12431</v>
       </c>
@@ -8725,7 +8727,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>12431</v>
       </c>
@@ -8781,7 +8783,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>12431</v>
       </c>
@@ -8837,7 +8839,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>12431</v>
       </c>
@@ -8893,7 +8895,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>12431</v>
       </c>
@@ -8949,7 +8951,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>12431</v>
       </c>
@@ -9005,7 +9007,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>12431</v>
       </c>
@@ -9061,7 +9063,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>12431</v>
       </c>
@@ -9121,7 +9123,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" ht="64.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>12431</v>
       </c>
@@ -9177,7 +9179,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>12431</v>
       </c>
@@ -9233,7 +9235,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>12431</v>
       </c>
@@ -9293,7 +9295,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>12431</v>
       </c>
@@ -9349,7 +9351,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>12431</v>
       </c>
@@ -9407,7 +9409,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>12431</v>
       </c>
@@ -9465,7 +9467,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>12431</v>
       </c>
@@ -9521,7 +9523,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>12431</v>
       </c>
@@ -9577,7 +9579,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>12431</v>
       </c>
@@ -9635,7 +9637,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>12431</v>
       </c>
@@ -9693,7 +9695,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>12431</v>
       </c>
@@ -9749,7 +9751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>12431</v>
       </c>
@@ -9809,7 +9811,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>12431</v>
       </c>
@@ -9867,7 +9869,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>12431</v>
       </c>
@@ -9925,7 +9927,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>12431</v>
       </c>
@@ -9979,7 +9981,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>12431</v>
       </c>
@@ -10033,7 +10035,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>12431</v>
       </c>
@@ -10089,7 +10091,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>12431</v>
       </c>
@@ -10143,7 +10145,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>12431</v>
       </c>
@@ -10199,7 +10201,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>12431</v>
       </c>
@@ -10255,7 +10257,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>12431</v>
       </c>
@@ -10309,7 +10311,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>12431</v>
       </c>
@@ -10365,7 +10367,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>12431</v>
       </c>
@@ -10421,7 +10423,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>12431</v>
       </c>
@@ -10477,7 +10479,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>12431</v>
       </c>
@@ -10533,7 +10535,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>12431</v>
       </c>
@@ -10589,7 +10591,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>12431</v>
       </c>
@@ -10649,7 +10651,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>12431</v>
       </c>
@@ -10819,7 +10821,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>12431</v>
       </c>
@@ -10873,7 +10875,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>12431</v>
       </c>
@@ -10927,7 +10929,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>12431</v>
       </c>
@@ -11103,7 +11105,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>12431</v>
       </c>
@@ -11163,7 +11165,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>12431</v>
       </c>
@@ -11223,7 +11225,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>12431</v>
       </c>
@@ -11283,7 +11285,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>12431</v>
       </c>
@@ -11339,7 +11341,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>12431</v>
       </c>
@@ -11395,7 +11397,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>12431</v>
       </c>
@@ -11453,7 +11455,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>12431</v>
       </c>
@@ -11509,7 +11511,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>12431</v>
       </c>
@@ -11569,7 +11571,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>12431</v>
       </c>
@@ -11627,7 +11629,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>12431</v>
       </c>
@@ -11687,7 +11689,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>12431</v>
       </c>
@@ -11745,7 +11747,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>12431</v>
       </c>
@@ -11805,7 +11807,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>12431</v>
       </c>
@@ -11865,7 +11867,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>12431</v>
       </c>
@@ -11925,7 +11927,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>12431</v>
       </c>
@@ -11981,7 +11983,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>12431</v>
       </c>
@@ -12037,7 +12039,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>12431</v>
       </c>
@@ -12097,7 +12099,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>12431</v>
       </c>
@@ -12157,7 +12159,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>12431</v>
       </c>
@@ -12217,7 +12219,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>12431</v>
       </c>
@@ -12275,7 +12277,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>12431</v>
       </c>
@@ -12333,7 +12335,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>12431</v>
       </c>
@@ -12389,7 +12391,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>12431</v>
       </c>
@@ -12445,7 +12447,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>12431</v>
       </c>
@@ -12503,7 +12505,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>12431</v>
       </c>
@@ -12561,7 +12563,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>12431</v>
       </c>
@@ -12621,7 +12623,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>12431</v>
       </c>
@@ -12681,7 +12683,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>12431</v>
       </c>
@@ -12735,7 +12737,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>12431</v>
       </c>
@@ -12789,7 +12791,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>12431</v>
       </c>
@@ -12847,7 +12849,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>12431</v>
       </c>
@@ -12905,7 +12907,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>12431</v>
       </c>
@@ -12963,7 +12965,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>12431</v>
       </c>
@@ -13019,7 +13021,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>12431</v>
       </c>
@@ -13075,7 +13077,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>12431</v>
       </c>
@@ -13131,7 +13133,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>12431</v>
       </c>
@@ -13187,7 +13189,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>12431</v>
       </c>
@@ -13243,7 +13245,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>12431</v>
       </c>
@@ -13303,7 +13305,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>12431</v>
       </c>
@@ -13363,7 +13365,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>12431</v>
       </c>
@@ -13423,7 +13425,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>12431</v>
       </c>
@@ -13479,7 +13481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>12431</v>
       </c>
@@ -13539,7 +13541,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>12431</v>
       </c>
@@ -13593,7 +13595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>12431</v>
       </c>
@@ -13649,7 +13651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>12431</v>
       </c>
@@ -13705,7 +13707,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:20" ht="113.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>12431</v>
       </c>
@@ -13761,7 +13763,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>12431</v>
       </c>
@@ -13935,7 +13937,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>12431</v>
       </c>
@@ -13993,7 +13995,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="185" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>12431</v>
       </c>
@@ -14049,7 +14051,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>12431</v>
       </c>
@@ -14105,7 +14107,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="187" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>12431</v>
       </c>
@@ -14161,7 +14163,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="188" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>12431</v>
       </c>
@@ -14331,7 +14333,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="191" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>12431</v>
       </c>
@@ -14387,7 +14389,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="192" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>12431</v>
       </c>
@@ -14443,7 +14445,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="193" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>12431</v>
       </c>
@@ -14497,7 +14499,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>12431</v>
       </c>
@@ -14551,7 +14553,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>12431</v>
       </c>
@@ -14609,7 +14611,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="196" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>12431</v>
       </c>
@@ -14669,7 +14671,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="197" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>12431</v>
       </c>
@@ -14725,7 +14727,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="198" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>12431</v>
       </c>
@@ -14781,7 +14783,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:20" ht="226.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>12431</v>
       </c>
@@ -14837,7 +14839,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>12431</v>
       </c>
@@ -14893,7 +14895,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>12431</v>
       </c>
@@ -14949,7 +14951,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>12431</v>
       </c>
@@ -15009,7 +15011,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="203" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>12431</v>
       </c>
@@ -15069,7 +15071,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>12431</v>
       </c>
@@ -15119,7 +15121,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="205" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>12431</v>
       </c>
@@ -15169,7 +15171,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="206" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>12431</v>
       </c>
@@ -15219,7 +15221,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="207" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>12431</v>
       </c>
@@ -15279,7 +15281,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="208" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>12431</v>
       </c>
@@ -15339,7 +15341,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="209" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>12431</v>
       </c>
@@ -15399,7 +15401,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="210" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>12431</v>
       </c>
@@ -15455,7 +15457,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="211" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>12431</v>
       </c>
@@ -15511,7 +15513,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>12431</v>
       </c>
@@ -15571,7 +15573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>12431</v>
       </c>
@@ -15625,7 +15627,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="214" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>12431</v>
       </c>
@@ -15679,7 +15681,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="215" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>12431</v>
       </c>
@@ -15735,7 +15737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>12431</v>
       </c>
@@ -15791,7 +15793,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="217" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>12431</v>
       </c>
@@ -15847,7 +15849,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="218" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>12431</v>
       </c>
@@ -15903,7 +15905,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="219" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>12431</v>
       </c>
@@ -15961,7 +15963,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="220" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>12431</v>
       </c>
@@ -16021,7 +16023,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="221" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>12431</v>
       </c>
@@ -16081,7 +16083,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="222" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:20" ht="81" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>12431</v>
       </c>
@@ -16137,7 +16139,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="223" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:20" ht="81" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>12431</v>
       </c>
@@ -16193,7 +16195,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="224" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:20" ht="81" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>12431</v>
       </c>
@@ -16249,7 +16251,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="225" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>12431</v>
       </c>
@@ -16305,7 +16307,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="226" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>12431</v>
       </c>
@@ -16361,7 +16363,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="227" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>12431</v>
       </c>
@@ -16419,7 +16421,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="228" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>12431</v>
       </c>
@@ -16479,7 +16481,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="229" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>12431</v>
       </c>
@@ -16537,7 +16539,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="230" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>12431</v>
       </c>
@@ -16595,7 +16597,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="231" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>12431</v>
       </c>
@@ -16653,7 +16655,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="232" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>12431</v>
       </c>
@@ -16709,7 +16711,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="233" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>12431</v>
       </c>
@@ -16767,7 +16769,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="234" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>12431</v>
       </c>
@@ -16823,7 +16825,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="235" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>12431</v>
       </c>
@@ -16879,7 +16881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="236" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>12431</v>
       </c>
@@ -16939,7 +16941,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="237" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>12431</v>
       </c>
@@ -17001,7 +17003,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="238" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>12431</v>
       </c>
@@ -17063,7 +17065,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="239" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>12431</v>
       </c>
@@ -17119,7 +17121,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="240" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>12431</v>
       </c>
@@ -17175,7 +17177,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="241" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>12431</v>
       </c>
@@ -17231,7 +17233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>12431</v>
       </c>
@@ -17461,7 +17463,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>12431</v>
       </c>
@@ -17523,7 +17525,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="247" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>12431</v>
       </c>
@@ -17585,7 +17587,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="248" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>12431</v>
       </c>
@@ -17643,7 +17645,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="249" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>12431</v>
       </c>
@@ -17701,7 +17703,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="250" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:20" ht="64.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>12431</v>
       </c>
@@ -17759,7 +17761,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>12431</v>
       </c>
@@ -17817,7 +17819,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>12431</v>
       </c>
@@ -17875,7 +17877,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="253" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>12431</v>
       </c>
@@ -17933,7 +17935,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="254" spans="1:20" ht="210.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:20" ht="48.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>12431</v>
       </c>
@@ -17995,7 +17997,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="255" spans="1:20" ht="194.4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>12431</v>
       </c>
@@ -18057,7 +18059,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="256" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>12431</v>
       </c>
@@ -18115,7 +18117,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="257" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:20" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>12431</v>
       </c>
@@ -18239,7 +18241,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="259" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>12431</v>
       </c>
@@ -18295,7 +18297,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="260" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>12431</v>
       </c>
@@ -18355,7 +18357,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="261" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>12431</v>
       </c>
@@ -18409,7 +18411,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="262" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>12431</v>
       </c>
@@ -18465,7 +18467,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="263" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>12431</v>
       </c>
@@ -18525,7 +18527,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="264" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>12431</v>
       </c>
@@ -18585,7 +18587,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="265" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>12431</v>
       </c>
@@ -18645,7 +18647,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="266" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>12431</v>
       </c>
@@ -18759,7 +18761,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="268" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>12431</v>
       </c>
@@ -18819,7 +18821,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="269" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>12431</v>
       </c>
@@ -18877,7 +18879,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="270" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>12431</v>
       </c>
@@ -18937,7 +18939,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="271" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>12431</v>
       </c>
@@ -18997,7 +18999,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="272" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>12431</v>
       </c>
@@ -19057,7 +19059,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="273" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>12431</v>
       </c>
@@ -19117,7 +19119,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="274" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>12431</v>
       </c>
@@ -19173,7 +19175,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="275" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:20" ht="81" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>12431</v>
       </c>
@@ -19229,7 +19231,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="276" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>12431</v>
       </c>
@@ -19289,7 +19291,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="277" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>12431</v>
       </c>
@@ -19351,7 +19353,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="278" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>12431</v>
       </c>
@@ -19413,7 +19415,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="279" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>12431</v>
       </c>
@@ -19471,7 +19473,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="280" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>12431</v>
       </c>
@@ -19527,7 +19529,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="281" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>12431</v>
       </c>
@@ -19583,7 +19585,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="282" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>12431</v>
       </c>
@@ -19641,7 +19643,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="283" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>12431</v>
       </c>
@@ -19699,7 +19701,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="284" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>12431</v>
       </c>
@@ -19755,7 +19757,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="285" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>12431</v>
       </c>
@@ -19815,7 +19817,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="286" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>12431</v>
       </c>
@@ -19873,7 +19875,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="287" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>12431</v>
       </c>
@@ -19931,7 +19933,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="288" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:20" ht="32.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>12431</v>
       </c>
@@ -19989,7 +19991,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>12431</v>
       </c>
@@ -20033,7 +20035,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -20046,7 +20048,7 @@
       <c r="M290" s="1"/>
       <c r="N290" s="3"/>
     </row>
-    <row r="291" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -20059,55 +20061,55 @@
       <c r="M291" s="1"/>
       <c r="N291" s="3"/>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L292" s="13"/>
       <c r="M292" s="14"/>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L293" s="13"/>
       <c r="M293" s="14"/>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L294" s="13"/>
       <c r="M294" s="14"/>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L295" s="13"/>
       <c r="M295" s="14"/>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L296" s="13"/>
       <c r="M296" s="14"/>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L297" s="13"/>
       <c r="M297" s="14"/>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L298" s="13"/>
       <c r="M298" s="14"/>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L299" s="13"/>
       <c r="M299" s="14"/>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L300" s="13"/>
       <c r="M300" s="14"/>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L301" s="13"/>
       <c r="M301" s="14"/>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L302" s="13"/>
       <c r="M302" s="14"/>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="L303" s="13"/>
       <c r="M303" s="14"/>
     </row>
-    <row r="304" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:20" ht="16.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="15"/>
       <c r="B304" s="16"/>
       <c r="C304" s="17"/>
@@ -20130,6 +20132,13 @@
       <c r="T304" s="15"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T304" xr:uid="{43430540-BBA7-4347-B81D-8C67916B1A6D}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Aemstel Schooltuin"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="M1:M304">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"ENGELS"</formula>
